--- a/research/traditional_assets/database/data/brazil/brazil_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_retail_building_supply.xlsx
@@ -1647,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1784,22 +1784,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1189198468944334</v>
+        <v>0.1185452194149923</v>
       </c>
       <c r="C2">
-        <v>380.000726415</v>
+        <v>376.9403984938261</v>
       </c>
       <c r="D2">
-        <v>291.400726415</v>
+        <v>292.901398493826</v>
       </c>
       <c r="E2">
-        <v>-388</v>
+        <v>-383.439</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.561</v>
       </c>
       <c r="G2">
         <v>88.59999999999999</v>
@@ -1820,28 +1820,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2294183</v>
       </c>
       <c r="N2">
-        <v>46.86666666666667</v>
+        <v>46.63724836666668</v>
       </c>
       <c r="O2">
-        <v>15.93466666666667</v>
+        <v>15.85666444466667</v>
       </c>
       <c r="P2">
-        <v>30.932</v>
+        <v>30.78058392200001</v>
       </c>
       <c r="Q2">
-        <v>39.232</v>
+        <v>39.080583922</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1189198468944334</v>
+        <v>0.1194073125403963</v>
       </c>
       <c r="T2">
-        <v>0.952996724804112</v>
+        <v>0.959350036302806</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>204.2847787934383</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1866,22 +1866,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1185452194149923</v>
+        <v>0.1181705919355513</v>
       </c>
       <c r="C3">
-        <v>376.9403984938261</v>
+        <v>373.8956070767297</v>
       </c>
       <c r="D3">
-        <v>292.901398493826</v>
+        <v>294.4176070767298</v>
       </c>
       <c r="E3">
-        <v>-383.439</v>
+        <v>-378.878</v>
       </c>
       <c r="F3">
-        <v>4.561</v>
+        <v>9.122</v>
       </c>
       <c r="G3">
         <v>88.59999999999999</v>
@@ -1902,28 +1902,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M3">
-        <v>0.2294183</v>
+        <v>0.4588366</v>
       </c>
       <c r="N3">
-        <v>46.63724836666668</v>
+        <v>46.40783006666668</v>
       </c>
       <c r="O3">
-        <v>15.85666444466667</v>
+        <v>15.77866222266667</v>
       </c>
       <c r="P3">
-        <v>30.78058392200001</v>
+        <v>30.629167844</v>
       </c>
       <c r="Q3">
-        <v>39.080583922</v>
+        <v>38.92916784400001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1194073125403963</v>
+        <v>0.1199047264648482</v>
       </c>
       <c r="T3">
-        <v>0.959350036302806</v>
+        <v>0.9658330072198408</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>204.2847787934383</v>
+        <v>102.1423893967192</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1948,22 +1948,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1181705919355513</v>
+        <v>0.1177959644561102</v>
       </c>
       <c r="C4">
-        <v>373.8956070767297</v>
+        <v>370.8665946940283</v>
       </c>
       <c r="D4">
-        <v>294.4176070767298</v>
+        <v>295.9495946940283</v>
       </c>
       <c r="E4">
-        <v>-378.878</v>
+        <v>-374.317</v>
       </c>
       <c r="F4">
-        <v>9.122</v>
+        <v>13.683</v>
       </c>
       <c r="G4">
         <v>88.59999999999999</v>
@@ -1984,28 +1984,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M4">
-        <v>0.4588366</v>
+        <v>0.6882549</v>
       </c>
       <c r="N4">
-        <v>46.40783006666668</v>
+        <v>46.17841176666668</v>
       </c>
       <c r="O4">
-        <v>15.77866222266667</v>
+        <v>15.70066000066667</v>
       </c>
       <c r="P4">
-        <v>30.629167844</v>
+        <v>30.477751766</v>
       </c>
       <c r="Q4">
-        <v>38.92916784400001</v>
+        <v>38.77775176600001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1199047264648482</v>
+        <v>0.1204123963465054</v>
       </c>
       <c r="T4">
-        <v>0.9658330072198408</v>
+        <v>0.9724496476403197</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.1423893967192</v>
+        <v>68.09492626447945</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2030,22 +2030,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1177959644561102</v>
+        <v>0.1174213369766691</v>
       </c>
       <c r="C5">
-        <v>370.8665946940283</v>
+        <v>367.8536089504215</v>
       </c>
       <c r="D5">
-        <v>295.9495946940283</v>
+        <v>297.4976089504216</v>
       </c>
       <c r="E5">
-        <v>-374.317</v>
+        <v>-369.756</v>
       </c>
       <c r="F5">
-        <v>13.683</v>
+        <v>18.244</v>
       </c>
       <c r="G5">
         <v>88.59999999999999</v>
@@ -2066,28 +2066,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M5">
-        <v>0.6882549</v>
+        <v>0.9176732</v>
       </c>
       <c r="N5">
-        <v>46.17841176666668</v>
+        <v>45.94899346666667</v>
       </c>
       <c r="O5">
-        <v>15.70066000066667</v>
+        <v>15.62265777866667</v>
       </c>
       <c r="P5">
-        <v>30.477751766</v>
+        <v>30.326335688</v>
       </c>
       <c r="Q5">
-        <v>38.77775176600001</v>
+        <v>38.626335688</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1204123963465054</v>
+        <v>0.1209306426840303</v>
       </c>
       <c r="T5">
-        <v>0.9724496476403197</v>
+        <v>0.9792041347362251</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.09492626447945</v>
+        <v>51.07119469835958</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2112,22 +2112,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1174213369766691</v>
+        <v>0.1170467094972281</v>
       </c>
       <c r="C6">
-        <v>367.8536089504215</v>
+        <v>364.8569026584022</v>
       </c>
       <c r="D6">
-        <v>297.4976089504216</v>
+        <v>299.0619026584022</v>
       </c>
       <c r="E6">
-        <v>-369.756</v>
+        <v>-365.195</v>
       </c>
       <c r="F6">
-        <v>18.244</v>
+        <v>22.805</v>
       </c>
       <c r="G6">
         <v>88.59999999999999</v>
@@ -2148,28 +2148,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M6">
-        <v>0.9176732</v>
+        <v>1.1470915</v>
       </c>
       <c r="N6">
-        <v>45.94899346666667</v>
+        <v>45.71957516666667</v>
       </c>
       <c r="O6">
-        <v>15.62265777866667</v>
+        <v>15.54465555666667</v>
       </c>
       <c r="P6">
-        <v>30.326335688</v>
+        <v>30.17491961</v>
       </c>
       <c r="Q6">
-        <v>38.626335688</v>
+        <v>38.47491961</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1209306426840303</v>
+        <v>0.1214597994707664</v>
       </c>
       <c r="T6">
-        <v>0.9792041347362251</v>
+        <v>0.9861008215604654</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.07119469835958</v>
+        <v>40.85695575868766</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2194,22 +2194,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1170467094972281</v>
+        <v>0.116672082017787</v>
       </c>
       <c r="C7">
-        <v>364.8569026584022</v>
+        <v>361.876733975897</v>
       </c>
       <c r="D7">
-        <v>299.0619026584022</v>
+        <v>300.6427339758969</v>
       </c>
       <c r="E7">
-        <v>-365.195</v>
+        <v>-360.634</v>
       </c>
       <c r="F7">
-        <v>22.805</v>
+        <v>27.366</v>
       </c>
       <c r="G7">
         <v>88.59999999999999</v>
@@ -2230,28 +2230,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M7">
-        <v>1.1470915</v>
+        <v>1.3765098</v>
       </c>
       <c r="N7">
-        <v>45.71957516666667</v>
+        <v>45.49015686666667</v>
       </c>
       <c r="O7">
-        <v>15.54465555666667</v>
+        <v>15.46665333466667</v>
       </c>
       <c r="P7">
-        <v>30.17491961</v>
+        <v>30.023503532</v>
       </c>
       <c r="Q7">
-        <v>38.47491961</v>
+        <v>38.323503532</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1214597994707664</v>
+        <v>0.1220002149125393</v>
       </c>
       <c r="T7">
-        <v>0.9861008215604654</v>
+        <v>0.9931442464022427</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.85695575868766</v>
+        <v>34.04746313223972</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2276,22 +2276,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.116672082017787</v>
+        <v>0.1162974545383459</v>
       </c>
       <c r="C8">
-        <v>361.876733975897</v>
+        <v>358.9133665482957</v>
       </c>
       <c r="D8">
-        <v>300.6427339758969</v>
+        <v>302.2403665482958</v>
       </c>
       <c r="E8">
-        <v>-360.634</v>
+        <v>-356.073</v>
       </c>
       <c r="F8">
-        <v>27.366</v>
+        <v>31.927</v>
       </c>
       <c r="G8">
         <v>88.59999999999999</v>
@@ -2312,28 +2312,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M8">
-        <v>1.3765098</v>
+        <v>1.6059281</v>
       </c>
       <c r="N8">
-        <v>45.49015686666667</v>
+        <v>45.26073856666667</v>
       </c>
       <c r="O8">
-        <v>15.46665333466667</v>
+        <v>15.38865111266667</v>
       </c>
       <c r="P8">
-        <v>30.023503532</v>
+        <v>29.872087454</v>
       </c>
       <c r="Q8">
-        <v>38.323503532</v>
+        <v>38.17208745400001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1220002149125393</v>
+        <v>0.1225522521917698</v>
       </c>
       <c r="T8">
-        <v>0.9931442464022427</v>
+        <v>1.000339142745994</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.04746313223972</v>
+        <v>29.18353982763405</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2358,22 +2358,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1162974545383459</v>
+        <v>0.1159228270589048</v>
       </c>
       <c r="C9">
-        <v>358.9133665482957</v>
+        <v>355.9670696550347</v>
       </c>
       <c r="D9">
-        <v>302.2403665482958</v>
+        <v>303.8550696550347</v>
       </c>
       <c r="E9">
-        <v>-356.073</v>
+        <v>-351.512</v>
       </c>
       <c r="F9">
-        <v>31.927</v>
+        <v>36.488</v>
       </c>
       <c r="G9">
         <v>88.59999999999999</v>
@@ -2394,28 +2394,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M9">
-        <v>1.6059281</v>
+        <v>1.8353464</v>
       </c>
       <c r="N9">
-        <v>45.26073856666667</v>
+        <v>45.03132026666668</v>
       </c>
       <c r="O9">
-        <v>15.38865111266667</v>
+        <v>15.31064889066667</v>
       </c>
       <c r="P9">
-        <v>29.872087454</v>
+        <v>29.72067137600001</v>
       </c>
       <c r="Q9">
-        <v>38.17208745400001</v>
+        <v>38.02067137600001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1225522521917698</v>
+        <v>0.1231162902814183</v>
       </c>
       <c r="T9">
-        <v>1.000339142745994</v>
+        <v>1.007690449879826</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.18353982763405</v>
+        <v>25.53559734917979</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2440,22 +2440,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1159228270589048</v>
+        <v>0.1155481995794637</v>
       </c>
       <c r="C10">
-        <v>355.9670696550347</v>
+        <v>353.0381183609023</v>
       </c>
       <c r="D10">
-        <v>303.8550696550347</v>
+        <v>305.4871183609023</v>
       </c>
       <c r="E10">
-        <v>-351.512</v>
+        <v>-346.951</v>
       </c>
       <c r="F10">
-        <v>36.488</v>
+        <v>41.049</v>
       </c>
       <c r="G10">
         <v>88.59999999999999</v>
@@ -2476,28 +2476,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M10">
-        <v>1.8353464</v>
+        <v>2.0647647</v>
       </c>
       <c r="N10">
-        <v>45.03132026666668</v>
+        <v>44.80190196666668</v>
       </c>
       <c r="O10">
-        <v>15.31064889066667</v>
+        <v>15.23264666866667</v>
       </c>
       <c r="P10">
-        <v>29.72067137600001</v>
+        <v>29.56925529800001</v>
       </c>
       <c r="Q10">
-        <v>38.02067137600001</v>
+        <v>37.86925529800001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1231162902814183</v>
+        <v>0.1236927248125975</v>
       </c>
       <c r="T10">
-        <v>1.007690449879826</v>
+        <v>1.015203324203413</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.53559734917979</v>
+        <v>22.69830875482648</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2522,22 +2522,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1155481995794637</v>
+        <v>0.1151735721000227</v>
       </c>
       <c r="C11">
-        <v>353.0381183609023</v>
+        <v>350.1267936722479</v>
       </c>
       <c r="D11">
-        <v>305.4871183609023</v>
+        <v>307.136793672248</v>
       </c>
       <c r="E11">
-        <v>-346.951</v>
+        <v>-342.39</v>
       </c>
       <c r="F11">
-        <v>41.049</v>
+        <v>45.61</v>
       </c>
       <c r="G11">
         <v>88.59999999999999</v>
@@ -2558,28 +2558,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M11">
-        <v>2.0647647</v>
+        <v>2.294183</v>
       </c>
       <c r="N11">
-        <v>44.80190196666668</v>
+        <v>44.57248366666668</v>
       </c>
       <c r="O11">
-        <v>15.23264666866667</v>
+        <v>15.15464444666667</v>
       </c>
       <c r="P11">
-        <v>29.56925529800001</v>
+        <v>29.41783922</v>
       </c>
       <c r="Q11">
-        <v>37.86925529800001</v>
+        <v>37.71783922</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1236927248125975</v>
+        <v>0.1242819690000252</v>
       </c>
       <c r="T11">
-        <v>1.015203324203413</v>
+        <v>1.022883151289747</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.69830875482648</v>
+        <v>20.42847787934384</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2604,22 +2604,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1151735721000227</v>
+        <v>0.1147989446205816</v>
       </c>
       <c r="C12">
-        <v>350.1267936722479</v>
+        <v>347.2333826982796</v>
       </c>
       <c r="D12">
-        <v>307.136793672248</v>
+        <v>308.8043826982796</v>
       </c>
       <c r="E12">
-        <v>-342.39</v>
+        <v>-337.829</v>
       </c>
       <c r="F12">
-        <v>45.61000000000001</v>
+        <v>50.171</v>
       </c>
       <c r="G12">
         <v>88.59999999999999</v>
@@ -2640,28 +2640,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M12">
-        <v>2.294183</v>
+        <v>2.5236013</v>
       </c>
       <c r="N12">
-        <v>44.57248366666667</v>
+        <v>44.34306536666667</v>
       </c>
       <c r="O12">
-        <v>15.15464444666667</v>
+        <v>15.07664222466667</v>
       </c>
       <c r="P12">
-        <v>29.41783922</v>
+        <v>29.266423142</v>
       </c>
       <c r="Q12">
-        <v>37.71783922</v>
+        <v>37.566423142</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1242819690000252</v>
+        <v>0.124884454629867</v>
       </c>
       <c r="T12">
-        <v>1.022883151289747</v>
+        <v>1.030735558760043</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.42847787934383</v>
+        <v>18.57134352667621</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2686,22 +2686,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1147989446205816</v>
+        <v>0.1144243171411406</v>
       </c>
       <c r="C13">
-        <v>347.2333826982796</v>
+        <v>344.3581788176446</v>
       </c>
       <c r="D13">
-        <v>308.8043826982796</v>
+        <v>310.4901788176446</v>
       </c>
       <c r="E13">
-        <v>-337.829</v>
+        <v>-333.268</v>
       </c>
       <c r="F13">
-        <v>50.171</v>
+        <v>54.732</v>
       </c>
       <c r="G13">
         <v>88.59999999999999</v>
@@ -2722,28 +2722,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M13">
-        <v>2.5236013</v>
+        <v>2.7530196</v>
       </c>
       <c r="N13">
-        <v>44.34306536666667</v>
+        <v>44.11364706666667</v>
       </c>
       <c r="O13">
-        <v>15.07664222466667</v>
+        <v>14.99864000266667</v>
       </c>
       <c r="P13">
-        <v>29.266423142</v>
+        <v>29.115007064</v>
       </c>
       <c r="Q13">
-        <v>37.566423142</v>
+        <v>37.41500706400001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.124884454629867</v>
+        <v>0.1255006331149325</v>
       </c>
       <c r="T13">
-        <v>1.030735558760043</v>
+        <v>1.038766430036482</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.57134352667621</v>
+        <v>17.02373156611986</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2768,22 +2768,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1144243171411406</v>
+        <v>0.1140496896616995</v>
       </c>
       <c r="C14">
-        <v>344.3581788176446</v>
+        <v>341.5014818504969</v>
       </c>
       <c r="D14">
-        <v>310.4901788176446</v>
+        <v>312.194481850497</v>
       </c>
       <c r="E14">
-        <v>-333.268</v>
+        <v>-328.707</v>
       </c>
       <c r="F14">
-        <v>54.732</v>
+        <v>59.29300000000001</v>
       </c>
       <c r="G14">
         <v>88.59999999999999</v>
@@ -2804,28 +2804,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M14">
-        <v>2.7530196</v>
+        <v>2.9824379</v>
       </c>
       <c r="N14">
-        <v>44.11364706666667</v>
+        <v>43.88422876666667</v>
       </c>
       <c r="O14">
-        <v>14.99864000266667</v>
+        <v>14.92063778066667</v>
       </c>
       <c r="P14">
-        <v>29.115007064</v>
+        <v>28.963590986</v>
       </c>
       <c r="Q14">
-        <v>37.41500706400001</v>
+        <v>37.263590986</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1255006331149325</v>
+        <v>0.1261309766226431</v>
       </c>
       <c r="T14">
-        <v>1.038766430036482</v>
+        <v>1.046981919043414</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.02373156611986</v>
+        <v>15.71421375334141</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2850,22 +2850,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1140496896616995</v>
+        <v>0.1136750621822584</v>
       </c>
       <c r="C15">
-        <v>341.5014818504969</v>
+        <v>338.663598236262</v>
       </c>
       <c r="D15">
-        <v>312.194481850497</v>
+        <v>313.9175982362619</v>
       </c>
       <c r="E15">
-        <v>-328.707</v>
+        <v>-324.146</v>
       </c>
       <c r="F15">
-        <v>59.29300000000001</v>
+        <v>63.85400000000001</v>
       </c>
       <c r="G15">
         <v>88.59999999999999</v>
@@ -2886,28 +2886,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M15">
-        <v>2.9824379</v>
+        <v>3.2118562</v>
       </c>
       <c r="N15">
-        <v>43.88422876666667</v>
+        <v>43.65481046666667</v>
       </c>
       <c r="O15">
-        <v>14.92063778066667</v>
+        <v>14.84263555866667</v>
       </c>
       <c r="P15">
-        <v>28.963590986</v>
+        <v>28.812174908</v>
       </c>
       <c r="Q15">
-        <v>37.263590986</v>
+        <v>37.112174908</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1261309766226431</v>
+        <v>0.1267759792816958</v>
       </c>
       <c r="T15">
-        <v>1.046981919043414</v>
+        <v>1.055388465934228</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.71421375334141</v>
+        <v>14.59176991381702</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2932,22 +2932,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1136750621822584</v>
+        <v>0.1133004347028173</v>
       </c>
       <c r="C16">
-        <v>338.663598236262</v>
+        <v>335.8448412173213</v>
       </c>
       <c r="D16">
-        <v>313.9175982362619</v>
+        <v>315.6598412173213</v>
       </c>
       <c r="E16">
-        <v>-324.146</v>
+        <v>-319.585</v>
       </c>
       <c r="F16">
-        <v>63.85400000000001</v>
+        <v>68.41500000000002</v>
       </c>
       <c r="G16">
         <v>88.59999999999999</v>
@@ -2968,28 +2968,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M16">
-        <v>3.2118562</v>
+        <v>3.441274500000001</v>
       </c>
       <c r="N16">
-        <v>43.65481046666667</v>
+        <v>43.42539216666668</v>
       </c>
       <c r="O16">
-        <v>14.84263555866667</v>
+        <v>14.76463333666667</v>
       </c>
       <c r="P16">
-        <v>28.812174908</v>
+        <v>28.66075883000001</v>
       </c>
       <c r="Q16">
-        <v>37.112174908</v>
+        <v>36.96075883</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1267759792816958</v>
+        <v>0.1274361584739027</v>
       </c>
       <c r="T16">
-        <v>1.055388465934228</v>
+        <v>1.063992813928356</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.59176991381702</v>
+        <v>13.61898525289589</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3014,22 +3014,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1133004347028173</v>
+        <v>0.1130842072233762</v>
       </c>
       <c r="C17">
-        <v>335.8448412173213</v>
+        <v>332.2982595280045</v>
       </c>
       <c r="D17">
-        <v>315.6598412173213</v>
+        <v>316.6742595280045</v>
       </c>
       <c r="E17">
-        <v>-319.585</v>
+        <v>-315.024</v>
       </c>
       <c r="F17">
-        <v>68.41500000000001</v>
+        <v>72.976</v>
       </c>
       <c r="G17">
         <v>88.59999999999999</v>
@@ -3050,45 +3050,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M17">
-        <v>3.4412745</v>
+        <v>3.7801568</v>
       </c>
       <c r="N17">
-        <v>43.42539216666668</v>
+        <v>43.08650986666667</v>
       </c>
       <c r="O17">
-        <v>14.76463333666667</v>
+        <v>14.64941335466667</v>
       </c>
       <c r="P17">
-        <v>28.66075883000001</v>
+        <v>28.437096512</v>
       </c>
       <c r="Q17">
-        <v>36.96075883</v>
+        <v>36.73709651200001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1274361584739027</v>
+        <v>0.128112056218305</v>
       </c>
       <c r="T17">
-        <v>1.063992813928356</v>
+        <v>1.072802027350915</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.34</v>
       </c>
       <c r="W17">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.61898525289589</v>
+        <v>12.39807477474656</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3096,22 +3096,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1130842072233762</v>
+        <v>0.1127194797439352</v>
       </c>
       <c r="C18">
-        <v>332.2982595280045</v>
+        <v>329.4632114469894</v>
       </c>
       <c r="D18">
-        <v>316.6742595280045</v>
+        <v>318.4002114469894</v>
       </c>
       <c r="E18">
-        <v>-315.024</v>
+        <v>-310.463</v>
       </c>
       <c r="F18">
-        <v>72.976</v>
+        <v>77.53700000000001</v>
       </c>
       <c r="G18">
         <v>88.59999999999999</v>
@@ -3132,28 +3132,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M18">
-        <v>3.7801568</v>
+        <v>4.0164166</v>
       </c>
       <c r="N18">
-        <v>43.08650986666667</v>
+        <v>42.85025006666667</v>
       </c>
       <c r="O18">
-        <v>14.64941335466667</v>
+        <v>14.56908502266667</v>
       </c>
       <c r="P18">
-        <v>28.437096512</v>
+        <v>28.28116504400001</v>
       </c>
       <c r="Q18">
-        <v>36.73709651200001</v>
+        <v>36.581165044</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.128112056218305</v>
+        <v>0.1288042406553436</v>
       </c>
       <c r="T18">
-        <v>1.072802027350915</v>
+        <v>1.081823510976427</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.39807477474656</v>
+        <v>11.668776258585</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3178,22 +3178,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1127194797439352</v>
+        <v>0.1123547522644941</v>
       </c>
       <c r="C19">
-        <v>329.4632114469894</v>
+        <v>326.6470801847326</v>
       </c>
       <c r="D19">
-        <v>318.4002114469894</v>
+        <v>320.1450801847326</v>
       </c>
       <c r="E19">
-        <v>-310.463</v>
+        <v>-305.902</v>
       </c>
       <c r="F19">
-        <v>77.53700000000001</v>
+        <v>82.09800000000001</v>
       </c>
       <c r="G19">
         <v>88.59999999999999</v>
@@ -3214,28 +3214,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M19">
-        <v>4.0164166</v>
+        <v>4.2526764</v>
       </c>
       <c r="N19">
-        <v>42.85025006666667</v>
+        <v>42.61399026666668</v>
       </c>
       <c r="O19">
-        <v>14.56908502266667</v>
+        <v>14.48875669066667</v>
       </c>
       <c r="P19">
-        <v>28.28116504400001</v>
+        <v>28.12523357600001</v>
       </c>
       <c r="Q19">
-        <v>36.581165044</v>
+        <v>36.42523357600001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1288042406553436</v>
+        <v>0.129513307639627</v>
       </c>
       <c r="T19">
-        <v>1.081823510976427</v>
+        <v>1.091065030787927</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.668776258585</v>
+        <v>11.02051091088583</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3260,22 +3260,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1123547522644941</v>
+        <v>0.111990024785053</v>
       </c>
       <c r="C20">
-        <v>326.6470801847326</v>
+        <v>323.8501784537758</v>
       </c>
       <c r="D20">
-        <v>320.1450801847326</v>
+        <v>321.9091784537758</v>
       </c>
       <c r="E20">
-        <v>-305.902</v>
+        <v>-301.341</v>
       </c>
       <c r="F20">
-        <v>82.098</v>
+        <v>86.65900000000001</v>
       </c>
       <c r="G20">
         <v>88.59999999999999</v>
@@ -3296,28 +3296,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M20">
-        <v>4.252676399999999</v>
+        <v>4.4889362</v>
       </c>
       <c r="N20">
-        <v>42.61399026666668</v>
+        <v>42.37773046666668</v>
       </c>
       <c r="O20">
-        <v>14.48875669066667</v>
+        <v>14.40842835866667</v>
       </c>
       <c r="P20">
-        <v>28.12523357600001</v>
+        <v>27.96930210800001</v>
       </c>
       <c r="Q20">
-        <v>36.42523357600001</v>
+        <v>36.26930210800001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.129513307639627</v>
+        <v>0.1302398824506827</v>
       </c>
       <c r="T20">
-        <v>1.091065030787927</v>
+        <v>1.100534736273786</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.02051091088583</v>
+        <v>10.44048402083921</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3342,22 +3342,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.111990024785053</v>
+        <v>0.111625297305612</v>
       </c>
       <c r="C21">
-        <v>323.8501784537758</v>
+        <v>321.0728258974218</v>
       </c>
       <c r="D21">
-        <v>321.9091784537758</v>
+        <v>323.6928258974218</v>
       </c>
       <c r="E21">
-        <v>-301.341</v>
+        <v>-296.78</v>
       </c>
       <c r="F21">
-        <v>86.65900000000001</v>
+        <v>91.22000000000001</v>
       </c>
       <c r="G21">
         <v>88.59999999999999</v>
@@ -3378,28 +3378,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M21">
-        <v>4.4889362</v>
+        <v>4.725196</v>
       </c>
       <c r="N21">
-        <v>42.37773046666668</v>
+        <v>42.14147066666668</v>
       </c>
       <c r="O21">
-        <v>14.40842835866667</v>
+        <v>14.32810002666667</v>
       </c>
       <c r="P21">
-        <v>27.96930210800001</v>
+        <v>27.81337064000001</v>
       </c>
       <c r="Q21">
-        <v>36.26930210800001</v>
+        <v>36.11337064000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1302398824506827</v>
+        <v>0.1309846216320149</v>
       </c>
       <c r="T21">
-        <v>1.100534736273786</v>
+        <v>1.110241184396791</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.44048402083921</v>
+        <v>9.918459819797247</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3424,22 +3424,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.111625297305612</v>
+        <v>0.1114961898261709</v>
       </c>
       <c r="C22">
-        <v>321.0728258974218</v>
+        <v>317.1479535781191</v>
       </c>
       <c r="D22">
-        <v>323.6928258974218</v>
+        <v>324.3289535781192</v>
       </c>
       <c r="E22">
-        <v>-296.78</v>
+        <v>-292.219</v>
       </c>
       <c r="F22">
-        <v>91.22000000000001</v>
+        <v>95.78100000000002</v>
       </c>
       <c r="G22">
         <v>88.59999999999999</v>
@@ -3460,45 +3460,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M22">
-        <v>4.725196</v>
+        <v>5.124283500000001</v>
       </c>
       <c r="N22">
-        <v>42.14147066666668</v>
+        <v>41.74238316666667</v>
       </c>
       <c r="O22">
-        <v>14.32810002666667</v>
+        <v>14.19241027666667</v>
       </c>
       <c r="P22">
-        <v>27.81337064000001</v>
+        <v>27.54997289</v>
       </c>
       <c r="Q22">
-        <v>36.11337064000001</v>
+        <v>35.84997289</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1309846216320149</v>
+        <v>0.1317482149698365</v>
       </c>
       <c r="T22">
-        <v>1.110241184396791</v>
+        <v>1.120193365383669</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.34</v>
       </c>
       <c r="W22">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.918459819797247</v>
+        <v>9.145994101744501</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3506,22 +3506,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1114961898261708</v>
+        <v>0.1111426823467298</v>
       </c>
       <c r="C23">
-        <v>317.1479535781193</v>
+        <v>314.3415909265032</v>
       </c>
       <c r="D23">
-        <v>324.3289535781193</v>
+        <v>326.0835909265031</v>
       </c>
       <c r="E23">
-        <v>-292.219</v>
+        <v>-287.658</v>
       </c>
       <c r="F23">
-        <v>95.78100000000001</v>
+        <v>100.342</v>
       </c>
       <c r="G23">
         <v>88.59999999999999</v>
@@ -3542,28 +3542,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M23">
-        <v>5.124283500000001</v>
+        <v>5.368297</v>
       </c>
       <c r="N23">
-        <v>41.74238316666667</v>
+        <v>41.49836966666668</v>
       </c>
       <c r="O23">
-        <v>14.19241027666667</v>
+        <v>14.10944568666667</v>
       </c>
       <c r="P23">
-        <v>27.54997289</v>
+        <v>27.38892398</v>
       </c>
       <c r="Q23">
-        <v>35.84997289</v>
+        <v>35.68892398000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1317482149698365</v>
+        <v>0.1325313876240126</v>
       </c>
       <c r="T23">
-        <v>1.120193365383669</v>
+        <v>1.130400730498416</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.145994101744501</v>
+        <v>8.730267097119754</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3588,22 +3588,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1111426823467298</v>
+        <v>0.1107891748672887</v>
       </c>
       <c r="C24">
-        <v>314.3415909265032</v>
+        <v>311.5543169131912</v>
       </c>
       <c r="D24">
-        <v>326.0835909265031</v>
+        <v>327.8573169131913</v>
       </c>
       <c r="E24">
-        <v>-287.658</v>
+        <v>-283.097</v>
       </c>
       <c r="F24">
-        <v>100.342</v>
+        <v>104.903</v>
       </c>
       <c r="G24">
         <v>88.59999999999999</v>
@@ -3624,28 +3624,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M24">
-        <v>5.368297</v>
+        <v>5.6123105</v>
       </c>
       <c r="N24">
-        <v>41.49836966666668</v>
+        <v>41.25435616666667</v>
       </c>
       <c r="O24">
-        <v>14.10944568666667</v>
+        <v>14.02648109666667</v>
       </c>
       <c r="P24">
-        <v>27.38892398</v>
+        <v>27.22787507</v>
       </c>
       <c r="Q24">
-        <v>35.68892398000001</v>
+        <v>35.52787507000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1325313876240126</v>
+        <v>0.1333349024250503</v>
       </c>
       <c r="T24">
-        <v>1.130400730498416</v>
+        <v>1.14087322197978</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.730267097119754</v>
+        <v>8.350690266810197</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3670,22 +3670,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1107891748672887</v>
+        <v>0.1104356673878477</v>
       </c>
       <c r="C25">
-        <v>311.5543169131912</v>
+        <v>308.7864447387744</v>
       </c>
       <c r="D25">
-        <v>327.8573169131913</v>
+        <v>329.6504447387744</v>
       </c>
       <c r="E25">
-        <v>-283.097</v>
+        <v>-278.536</v>
       </c>
       <c r="F25">
-        <v>104.903</v>
+        <v>109.464</v>
       </c>
       <c r="G25">
         <v>88.59999999999999</v>
@@ -3706,28 +3706,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M25">
-        <v>5.6123105</v>
+        <v>5.856324000000001</v>
       </c>
       <c r="N25">
-        <v>41.25435616666667</v>
+        <v>41.01034266666667</v>
       </c>
       <c r="O25">
-        <v>14.02648109666667</v>
+        <v>13.94351650666667</v>
       </c>
       <c r="P25">
-        <v>27.22787507</v>
+        <v>27.06682616000001</v>
       </c>
       <c r="Q25">
-        <v>35.52787507000001</v>
+        <v>35.36682616</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1333349024250503</v>
+        <v>0.1341595623524311</v>
       </c>
       <c r="T25">
-        <v>1.14087322197978</v>
+        <v>1.151621305342232</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.350690266810197</v>
+        <v>8.002744839026438</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3752,22 +3752,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1104356673878476</v>
+        <v>0.1100821599084066</v>
       </c>
       <c r="C26">
-        <v>308.7864447387745</v>
+        <v>306.038294493392</v>
       </c>
       <c r="D26">
-        <v>329.6504447387745</v>
+        <v>331.463294493392</v>
       </c>
       <c r="E26">
-        <v>-278.536</v>
+        <v>-273.975</v>
       </c>
       <c r="F26">
-        <v>109.464</v>
+        <v>114.025</v>
       </c>
       <c r="G26">
         <v>88.59999999999999</v>
@@ -3788,28 +3788,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M26">
-        <v>5.856324</v>
+        <v>6.1003375</v>
       </c>
       <c r="N26">
-        <v>41.01034266666667</v>
+        <v>40.76632916666667</v>
       </c>
       <c r="O26">
-        <v>13.94351650666667</v>
+        <v>13.86055191666667</v>
       </c>
       <c r="P26">
-        <v>27.06682616000001</v>
+        <v>26.90577725</v>
       </c>
       <c r="Q26">
-        <v>35.36682616</v>
+        <v>35.20577725</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1341595623524311</v>
+        <v>0.1350062132112088</v>
       </c>
       <c r="T26">
-        <v>1.151621305342232</v>
+        <v>1.162656004261017</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.002744839026439</v>
+        <v>7.682635045465381</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3834,22 +3834,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1100821599084066</v>
+        <v>0.1098659324289655</v>
       </c>
       <c r="C27">
-        <v>306.038294493392</v>
+        <v>302.5960087613065</v>
       </c>
       <c r="D27">
-        <v>331.463294493392</v>
+        <v>332.5820087613066</v>
       </c>
       <c r="E27">
-        <v>-273.975</v>
+        <v>-269.414</v>
       </c>
       <c r="F27">
-        <v>114.025</v>
+        <v>118.586</v>
       </c>
       <c r="G27">
         <v>88.59999999999999</v>
@@ -3870,45 +3870,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M27">
-        <v>6.1003375</v>
+        <v>6.439219800000001</v>
       </c>
       <c r="N27">
-        <v>40.76632916666667</v>
+        <v>40.42744686666667</v>
       </c>
       <c r="O27">
-        <v>13.86055191666667</v>
+        <v>13.74533193466667</v>
       </c>
       <c r="P27">
-        <v>26.90577725</v>
+        <v>26.682114932</v>
       </c>
       <c r="Q27">
-        <v>35.20577725</v>
+        <v>34.982114932</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1350062132112088</v>
+        <v>0.1358757465256291</v>
       </c>
       <c r="T27">
-        <v>1.162656004261017</v>
+        <v>1.173988938285714</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.34</v>
       </c>
       <c r="W27">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.682635045465381</v>
+        <v>7.278314473232714</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3916,22 +3916,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1098659324289655</v>
+        <v>0.1095177049495244</v>
       </c>
       <c r="C28">
-        <v>302.5960087613065</v>
+        <v>299.8526227935467</v>
       </c>
       <c r="D28">
-        <v>332.5820087613066</v>
+        <v>334.3996227935468</v>
       </c>
       <c r="E28">
-        <v>-269.414</v>
+        <v>-264.853</v>
       </c>
       <c r="F28">
-        <v>118.586</v>
+        <v>123.147</v>
       </c>
       <c r="G28">
         <v>88.59999999999999</v>
@@ -3952,28 +3952,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M28">
-        <v>6.439219800000001</v>
+        <v>6.686882100000001</v>
       </c>
       <c r="N28">
-        <v>40.42744686666667</v>
+        <v>40.17978456666668</v>
       </c>
       <c r="O28">
-        <v>13.74533193466667</v>
+        <v>13.66112675266667</v>
       </c>
       <c r="P28">
-        <v>26.682114932</v>
+        <v>26.518657814</v>
       </c>
       <c r="Q28">
-        <v>34.982114932</v>
+        <v>34.81865781400001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1358757465256291</v>
+        <v>0.1367691026705814</v>
       </c>
       <c r="T28">
-        <v>1.173988938285714</v>
+        <v>1.185632363653554</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.278314473232714</v>
+        <v>7.008747270520392</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3998,22 +3998,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1095177049495244</v>
+        <v>0.1091694774700834</v>
       </c>
       <c r="C29">
-        <v>299.8526227935467</v>
+        <v>297.1292131039042</v>
       </c>
       <c r="D29">
-        <v>334.3996227935468</v>
+        <v>336.2372131039043</v>
       </c>
       <c r="E29">
-        <v>-264.853</v>
+        <v>-260.292</v>
       </c>
       <c r="F29">
-        <v>123.147</v>
+        <v>127.708</v>
       </c>
       <c r="G29">
         <v>88.59999999999999</v>
@@ -4034,28 +4034,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M29">
-        <v>6.686882100000001</v>
+        <v>6.934544400000001</v>
       </c>
       <c r="N29">
-        <v>40.17978456666668</v>
+        <v>39.93212226666667</v>
       </c>
       <c r="O29">
-        <v>13.66112675266667</v>
+        <v>13.57692157066667</v>
       </c>
       <c r="P29">
-        <v>26.518657814</v>
+        <v>26.355200696</v>
       </c>
       <c r="Q29">
-        <v>34.81865781400001</v>
+        <v>34.65520069600001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1367691026705814</v>
+        <v>0.1376872742640047</v>
       </c>
       <c r="T29">
-        <v>1.185632363653554</v>
+        <v>1.197599217503834</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.008747270520392</v>
+        <v>6.758434868001807</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4080,22 +4080,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1091694774700834</v>
+        <v>0.1088212499906423</v>
       </c>
       <c r="C30">
-        <v>297.1292131039042</v>
+        <v>294.426110832541</v>
       </c>
       <c r="D30">
-        <v>336.2372131039043</v>
+        <v>338.095110832541</v>
       </c>
       <c r="E30">
-        <v>-260.292</v>
+        <v>-255.731</v>
       </c>
       <c r="F30">
-        <v>127.708</v>
+        <v>132.269</v>
       </c>
       <c r="G30">
         <v>88.59999999999999</v>
@@ -4116,28 +4116,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M30">
-        <v>6.934544400000001</v>
+        <v>7.182206700000002</v>
       </c>
       <c r="N30">
-        <v>39.93212226666667</v>
+        <v>39.68445996666667</v>
       </c>
       <c r="O30">
-        <v>13.57692157066667</v>
+        <v>13.49271638866667</v>
       </c>
       <c r="P30">
-        <v>26.355200696</v>
+        <v>26.191743578</v>
       </c>
       <c r="Q30">
-        <v>34.65520069600001</v>
+        <v>34.491743578</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1376872742640047</v>
+        <v>0.138631309845975</v>
       </c>
       <c r="T30">
-        <v>1.197599217503834</v>
+        <v>1.20990316582877</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.758434868001807</v>
+        <v>6.525385389794847</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4162,22 +4162,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1088212499906423</v>
+        <v>0.1084730225112012</v>
       </c>
       <c r="C31">
-        <v>294.426110832541</v>
+        <v>291.7436544792198</v>
       </c>
       <c r="D31">
-        <v>338.095110832541</v>
+        <v>339.9736544792198</v>
       </c>
       <c r="E31">
-        <v>-255.731</v>
+        <v>-251.17</v>
       </c>
       <c r="F31">
-        <v>132.269</v>
+        <v>136.83</v>
       </c>
       <c r="G31">
         <v>88.59999999999999</v>
@@ -4198,28 +4198,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M31">
-        <v>7.1822067</v>
+        <v>7.429869000000001</v>
       </c>
       <c r="N31">
-        <v>39.68445996666667</v>
+        <v>39.43679766666667</v>
       </c>
       <c r="O31">
-        <v>13.49271638866667</v>
+        <v>13.40851120666667</v>
       </c>
       <c r="P31">
-        <v>26.191743578</v>
+        <v>26.02828646</v>
       </c>
       <c r="Q31">
-        <v>34.491743578</v>
+        <v>34.32828646</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.138631309845975</v>
+        <v>0.1396023178731446</v>
       </c>
       <c r="T31">
-        <v>1.20990316582877</v>
+        <v>1.222558655534418</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.525385389794849</v>
+        <v>6.307872543468353</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4244,22 +4244,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1084730225112012</v>
+        <v>0.1083293950317601</v>
       </c>
       <c r="C32">
-        <v>291.7436544792198</v>
+        <v>287.963560148376</v>
       </c>
       <c r="D32">
-        <v>339.9736544792198</v>
+        <v>340.754560148376</v>
       </c>
       <c r="E32">
-        <v>-251.17</v>
+        <v>-246.609</v>
       </c>
       <c r="F32">
-        <v>136.83</v>
+        <v>141.391</v>
       </c>
       <c r="G32">
         <v>88.59999999999999</v>
@@ -4280,45 +4280,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M32">
-        <v>7.429869000000001</v>
+        <v>7.818922300000001</v>
       </c>
       <c r="N32">
-        <v>39.43679766666667</v>
+        <v>39.04774436666667</v>
       </c>
       <c r="O32">
-        <v>13.40851120666667</v>
+        <v>13.27623308466667</v>
       </c>
       <c r="P32">
-        <v>26.02828646</v>
+        <v>25.771511282</v>
       </c>
       <c r="Q32">
-        <v>34.32828646</v>
+        <v>34.071511282</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1396023178731446</v>
+        <v>0.140601471060522</v>
       </c>
       <c r="T32">
-        <v>1.222558655534418</v>
+        <v>1.235580971028636</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.34</v>
       </c>
       <c r="W32">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.307872543468353</v>
+        <v>5.994005934381349</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4326,22 +4326,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1083293950317601</v>
+        <v>0.1079877675523191</v>
       </c>
       <c r="C33">
-        <v>287.963560148376</v>
+        <v>285.2744897267069</v>
       </c>
       <c r="D33">
-        <v>340.754560148376</v>
+        <v>342.6264897267069</v>
       </c>
       <c r="E33">
-        <v>-246.609</v>
+        <v>-242.048</v>
       </c>
       <c r="F33">
-        <v>141.391</v>
+        <v>145.952</v>
       </c>
       <c r="G33">
         <v>88.59999999999999</v>
@@ -4362,28 +4362,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M33">
-        <v>7.818922300000001</v>
+        <v>8.071145599999999</v>
       </c>
       <c r="N33">
-        <v>39.04774436666667</v>
+        <v>38.79552106666667</v>
       </c>
       <c r="O33">
-        <v>13.27623308466667</v>
+        <v>13.19047716266667</v>
       </c>
       <c r="P33">
-        <v>25.771511282</v>
+        <v>25.60504390400001</v>
       </c>
       <c r="Q33">
-        <v>34.071511282</v>
+        <v>33.90504390400001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.140601471060522</v>
+        <v>0.1416300111063516</v>
       </c>
       <c r="T33">
-        <v>1.235580971028636</v>
+        <v>1.248986295802095</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.994005934381349</v>
+        <v>5.806693248931933</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4408,22 +4408,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1079877675523191</v>
+        <v>0.107646140072878</v>
       </c>
       <c r="C34">
-        <v>285.2744897267069</v>
+        <v>282.606099741449</v>
       </c>
       <c r="D34">
-        <v>342.6264897267069</v>
+        <v>344.5190997414491</v>
       </c>
       <c r="E34">
-        <v>-242.048</v>
+        <v>-237.487</v>
       </c>
       <c r="F34">
-        <v>145.952</v>
+        <v>150.513</v>
       </c>
       <c r="G34">
         <v>88.59999999999999</v>
@@ -4444,28 +4444,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M34">
-        <v>8.071145599999999</v>
+        <v>8.3233689</v>
       </c>
       <c r="N34">
-        <v>38.79552106666667</v>
+        <v>38.54329776666668</v>
       </c>
       <c r="O34">
-        <v>13.19047716266667</v>
+        <v>13.10472124066667</v>
       </c>
       <c r="P34">
-        <v>25.60504390400001</v>
+        <v>25.43857652600001</v>
       </c>
       <c r="Q34">
-        <v>33.90504390400001</v>
+        <v>33.738576526</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1416300111063516</v>
+        <v>0.1426892538401164</v>
       </c>
       <c r="T34">
-        <v>1.248986295802095</v>
+        <v>1.262791779524016</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.806693248931933</v>
+        <v>5.630732847449147</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4490,22 +4490,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.107646140072878</v>
+        <v>0.1073045125934369</v>
       </c>
       <c r="C35">
-        <v>282.606099741449</v>
+        <v>279.9587348017249</v>
       </c>
       <c r="D35">
-        <v>344.5190997414491</v>
+        <v>346.432734801725</v>
       </c>
       <c r="E35">
-        <v>-237.487</v>
+        <v>-232.926</v>
       </c>
       <c r="F35">
-        <v>150.513</v>
+        <v>155.074</v>
       </c>
       <c r="G35">
         <v>88.59999999999999</v>
@@ -4526,28 +4526,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M35">
-        <v>8.3233689</v>
+        <v>8.575592200000001</v>
       </c>
       <c r="N35">
-        <v>38.54329776666668</v>
+        <v>38.29107446666667</v>
       </c>
       <c r="O35">
-        <v>13.10472124066667</v>
+        <v>13.01896531866667</v>
       </c>
       <c r="P35">
-        <v>25.43857652600001</v>
+        <v>25.272109148</v>
       </c>
       <c r="Q35">
-        <v>33.738576526</v>
+        <v>33.572109148</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1426892538401164</v>
+        <v>0.1437805948385408</v>
       </c>
       <c r="T35">
-        <v>1.262791779524016</v>
+        <v>1.27701561123751</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.630732847449147</v>
+        <v>5.465123057818289</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4572,22 +4572,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1073045125934369</v>
+        <v>0.1069628851139958</v>
       </c>
       <c r="C36">
-        <v>279.9587348017249</v>
+        <v>277.332747215963</v>
       </c>
       <c r="D36">
-        <v>346.432734801725</v>
+        <v>348.367747215963</v>
       </c>
       <c r="E36">
-        <v>-232.926</v>
+        <v>-228.365</v>
       </c>
       <c r="F36">
-        <v>155.074</v>
+        <v>159.635</v>
       </c>
       <c r="G36">
         <v>88.59999999999999</v>
@@ -4608,28 +4608,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M36">
-        <v>8.575592200000001</v>
+        <v>8.827815500000002</v>
       </c>
       <c r="N36">
-        <v>38.29107446666667</v>
+        <v>38.03885116666667</v>
       </c>
       <c r="O36">
-        <v>13.01896531866667</v>
+        <v>12.93320939666667</v>
       </c>
       <c r="P36">
-        <v>25.272109148</v>
+        <v>25.10564177000001</v>
       </c>
       <c r="Q36">
-        <v>33.572109148</v>
+        <v>33.40564177</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1437805948385408</v>
+        <v>0.1449055155599936</v>
       </c>
       <c r="T36">
-        <v>1.27701561123751</v>
+        <v>1.291677099311419</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.465123057818289</v>
+        <v>5.308976684737766</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4654,22 +4654,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1069628851139958</v>
+        <v>0.1066212576345548</v>
       </c>
       <c r="C37">
-        <v>277.332747215963</v>
+        <v>274.7284972081291</v>
       </c>
       <c r="D37">
-        <v>348.367747215963</v>
+        <v>350.3244972081291</v>
       </c>
       <c r="E37">
-        <v>-228.365</v>
+        <v>-223.804</v>
       </c>
       <c r="F37">
-        <v>159.635</v>
+        <v>164.196</v>
       </c>
       <c r="G37">
         <v>88.59999999999999</v>
@@ -4690,28 +4690,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M37">
-        <v>8.827815500000002</v>
+        <v>9.080038800000002</v>
       </c>
       <c r="N37">
-        <v>38.03885116666667</v>
+        <v>37.78662786666667</v>
       </c>
       <c r="O37">
-        <v>12.93320939666667</v>
+        <v>12.84745347466667</v>
       </c>
       <c r="P37">
-        <v>25.10564177000001</v>
+        <v>24.939174392</v>
       </c>
       <c r="Q37">
-        <v>33.40564177</v>
+        <v>33.239174392</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1449055155599936</v>
+        <v>0.1460655900539918</v>
       </c>
       <c r="T37">
-        <v>1.291677099311419</v>
+        <v>1.306796758887639</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.308976684737766</v>
+        <v>5.161505110161716</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4736,22 +4736,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1066212576345548</v>
+        <v>0.1062796301551137</v>
       </c>
       <c r="C38">
-        <v>274.7284972081289</v>
+        <v>272.1463531412875</v>
       </c>
       <c r="D38">
-        <v>350.324497208129</v>
+        <v>352.3033531412875</v>
       </c>
       <c r="E38">
-        <v>-223.804</v>
+        <v>-219.243</v>
       </c>
       <c r="F38">
-        <v>164.196</v>
+        <v>168.757</v>
       </c>
       <c r="G38">
         <v>88.59999999999999</v>
@@ -4772,28 +4772,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M38">
-        <v>9.080038800000001</v>
+        <v>9.332262100000001</v>
       </c>
       <c r="N38">
-        <v>37.78662786666668</v>
+        <v>37.53440456666667</v>
       </c>
       <c r="O38">
-        <v>12.84745347466667</v>
+        <v>12.76169755266667</v>
       </c>
       <c r="P38">
-        <v>24.93917439200001</v>
+        <v>24.77270701400001</v>
       </c>
       <c r="Q38">
-        <v>33.23917439200001</v>
+        <v>33.072707014</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1460655900539918</v>
+        <v>0.1472624923097043</v>
       </c>
       <c r="T38">
-        <v>1.306796758887639</v>
+        <v>1.322396407656753</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.161505110161718</v>
+        <v>5.022004972049238</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4818,22 +4818,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1062796301551137</v>
+        <v>0.1059380026756726</v>
       </c>
       <c r="C39">
-        <v>272.1463531412875</v>
+        <v>269.5866917487797</v>
       </c>
       <c r="D39">
-        <v>352.3033531412875</v>
+        <v>354.3046917487797</v>
       </c>
       <c r="E39">
-        <v>-219.243</v>
+        <v>-214.682</v>
       </c>
       <c r="F39">
-        <v>168.757</v>
+        <v>173.318</v>
       </c>
       <c r="G39">
         <v>88.59999999999999</v>
@@ -4854,28 +4854,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M39">
-        <v>9.332262100000001</v>
+        <v>9.5844854</v>
       </c>
       <c r="N39">
-        <v>37.53440456666667</v>
+        <v>37.28218126666668</v>
       </c>
       <c r="O39">
-        <v>12.76169755266667</v>
+        <v>12.67594163066667</v>
       </c>
       <c r="P39">
-        <v>24.77270701400001</v>
+        <v>24.60623963600001</v>
       </c>
       <c r="Q39">
-        <v>33.072707014</v>
+        <v>32.90623963600001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1472624923097043</v>
+        <v>0.148498004315601</v>
       </c>
       <c r="T39">
-        <v>1.322396407656753</v>
+        <v>1.338499270902292</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.022004972049238</v>
+        <v>4.889846946468996</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4900,22 +4900,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1059380026756726</v>
+        <v>0.1055963751962316</v>
       </c>
       <c r="C40">
-        <v>269.5866917487797</v>
+        <v>267.0498983733296</v>
       </c>
       <c r="D40">
-        <v>354.3046917487797</v>
+        <v>356.3288983733296</v>
       </c>
       <c r="E40">
-        <v>-214.682</v>
+        <v>-210.121</v>
       </c>
       <c r="F40">
-        <v>173.318</v>
+        <v>177.879</v>
       </c>
       <c r="G40">
         <v>88.59999999999999</v>
@@ -4936,28 +4936,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M40">
-        <v>9.5844854</v>
+        <v>9.836708700000001</v>
       </c>
       <c r="N40">
-        <v>37.28218126666668</v>
+        <v>37.02995796666667</v>
       </c>
       <c r="O40">
-        <v>12.67594163066667</v>
+        <v>12.59018570866667</v>
       </c>
       <c r="P40">
-        <v>24.60623963600001</v>
+        <v>24.439772258</v>
       </c>
       <c r="Q40">
-        <v>32.90623963600001</v>
+        <v>32.739772258</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.148498004315601</v>
+        <v>0.149774024911855</v>
       </c>
       <c r="T40">
-        <v>1.338499270902292</v>
+        <v>1.355130096877191</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.889846946468996</v>
+        <v>4.764466255533893</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4982,22 +4982,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1055963751962316</v>
+        <v>0.1052547477167905</v>
       </c>
       <c r="C41">
-        <v>267.0498983733296</v>
+        <v>264.536367214391</v>
       </c>
       <c r="D41">
-        <v>356.3288983733296</v>
+        <v>358.3763672143911</v>
       </c>
       <c r="E41">
-        <v>-210.121</v>
+        <v>-205.56</v>
       </c>
       <c r="F41">
-        <v>177.879</v>
+        <v>182.44</v>
       </c>
       <c r="G41">
         <v>88.59999999999999</v>
@@ -5018,28 +5018,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M41">
-        <v>9.836708700000001</v>
+        <v>10.088932</v>
       </c>
       <c r="N41">
-        <v>37.02995796666667</v>
+        <v>36.77773466666667</v>
       </c>
       <c r="O41">
-        <v>12.59018570866667</v>
+        <v>12.50442978666667</v>
       </c>
       <c r="P41">
-        <v>24.439772258</v>
+        <v>24.27330488</v>
       </c>
       <c r="Q41">
-        <v>32.739772258</v>
+        <v>32.57330488000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.149774024911855</v>
+        <v>0.1510925795279841</v>
       </c>
       <c r="T41">
-        <v>1.355130096877191</v>
+        <v>1.372315283717921</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.764466255533893</v>
+        <v>4.645354599145546</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5064,22 +5064,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1052547477167905</v>
+        <v>0.1049131202373494</v>
       </c>
       <c r="C42">
-        <v>264.536367214391</v>
+        <v>262.0465015840727</v>
       </c>
       <c r="D42">
-        <v>358.3763672143911</v>
+        <v>360.4475015840728</v>
       </c>
       <c r="E42">
-        <v>-205.56</v>
+        <v>-200.999</v>
       </c>
       <c r="F42">
-        <v>182.44</v>
+        <v>187.001</v>
       </c>
       <c r="G42">
         <v>88.59999999999999</v>
@@ -5100,28 +5100,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M42">
-        <v>10.088932</v>
+        <v>10.3411553</v>
       </c>
       <c r="N42">
-        <v>36.77773466666667</v>
+        <v>36.52551136666667</v>
       </c>
       <c r="O42">
-        <v>12.50442978666667</v>
+        <v>12.41867386466667</v>
       </c>
       <c r="P42">
-        <v>24.27330488</v>
+        <v>24.106837502</v>
       </c>
       <c r="Q42">
-        <v>32.57330488000001</v>
+        <v>32.406837502</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1510925795279841</v>
+        <v>0.1524558309107617</v>
       </c>
       <c r="T42">
-        <v>1.372315283717921</v>
+        <v>1.390083019265117</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.645354599145546</v>
+        <v>4.532053267459069</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5146,22 +5146,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1049131202373494</v>
+        <v>0.1052644927579083</v>
       </c>
       <c r="C43">
-        <v>262.0465015840727</v>
+        <v>255.3556364950625</v>
       </c>
       <c r="D43">
-        <v>360.4475015840728</v>
+        <v>358.3176364950626</v>
       </c>
       <c r="E43">
-        <v>-200.999</v>
+        <v>-196.438</v>
       </c>
       <c r="F43">
-        <v>187.001</v>
+        <v>191.562</v>
       </c>
       <c r="G43">
         <v>88.59999999999999</v>
@@ -5182,45 +5182,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M43">
-        <v>10.3411553</v>
+        <v>11.0722836</v>
       </c>
       <c r="N43">
-        <v>36.52551136666667</v>
+        <v>35.79438306666667</v>
       </c>
       <c r="O43">
-        <v>12.41867386466667</v>
+        <v>12.17009024266667</v>
       </c>
       <c r="P43">
-        <v>24.106837502</v>
+        <v>23.624292824</v>
       </c>
       <c r="Q43">
-        <v>32.406837502</v>
+        <v>31.924292824</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1524558309107617</v>
+        <v>0.1538660909619109</v>
       </c>
       <c r="T43">
-        <v>1.390083019265117</v>
+        <v>1.408463435348422</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.34</v>
       </c>
       <c r="W43">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.532053267459069</v>
+        <v>4.232791387918086</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5228,22 +5228,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1052644927579083</v>
+        <v>0.1049393652784673</v>
       </c>
       <c r="C44">
-        <v>255.3556364950625</v>
+        <v>252.7645411337811</v>
       </c>
       <c r="D44">
-        <v>358.3176364950626</v>
+        <v>360.2875411337811</v>
       </c>
       <c r="E44">
-        <v>-196.438</v>
+        <v>-191.877</v>
       </c>
       <c r="F44">
-        <v>191.562</v>
+        <v>196.123</v>
       </c>
       <c r="G44">
         <v>88.59999999999999</v>
@@ -5264,28 +5264,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M44">
-        <v>11.0722836</v>
+        <v>11.3359094</v>
       </c>
       <c r="N44">
-        <v>35.79438306666667</v>
+        <v>35.53075726666667</v>
       </c>
       <c r="O44">
-        <v>12.17009024266667</v>
+        <v>12.08045747066667</v>
       </c>
       <c r="P44">
-        <v>23.624292824</v>
+        <v>23.450299796</v>
       </c>
       <c r="Q44">
-        <v>31.924292824</v>
+        <v>31.750299796</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1538660909619109</v>
+        <v>0.1553258338218724</v>
       </c>
       <c r="T44">
-        <v>1.408463435348422</v>
+        <v>1.427488778311844</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.232791387918086</v>
+        <v>4.134354378896735</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5310,22 +5310,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1049393652784673</v>
+        <v>0.1046142377990262</v>
       </c>
       <c r="C45">
-        <v>252.7645411337811</v>
+        <v>250.1952251971387</v>
       </c>
       <c r="D45">
-        <v>360.2875411337811</v>
+        <v>362.2792251971387</v>
       </c>
       <c r="E45">
-        <v>-191.877</v>
+        <v>-187.316</v>
       </c>
       <c r="F45">
-        <v>196.123</v>
+        <v>200.684</v>
       </c>
       <c r="G45">
         <v>88.59999999999999</v>
@@ -5346,28 +5346,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M45">
-        <v>11.3359094</v>
+        <v>11.5995352</v>
       </c>
       <c r="N45">
-        <v>35.53075726666667</v>
+        <v>35.26713146666668</v>
       </c>
       <c r="O45">
-        <v>12.08045747066667</v>
+        <v>11.99082469866667</v>
       </c>
       <c r="P45">
-        <v>23.450299796</v>
+        <v>23.276306768</v>
       </c>
       <c r="Q45">
-        <v>31.750299796</v>
+        <v>31.57630676800001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1553258338218724</v>
+        <v>0.1568377103554039</v>
       </c>
       <c r="T45">
-        <v>1.427488778311844</v>
+        <v>1.447193597809673</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.134354378896735</v>
+        <v>4.040391779376356</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5392,22 +5392,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1046142377990262</v>
+        <v>0.1053286103195851</v>
       </c>
       <c r="C46">
-        <v>250.1952251971387</v>
+        <v>241.2866968093466</v>
       </c>
       <c r="D46">
-        <v>362.2792251971387</v>
+        <v>357.9316968093466</v>
       </c>
       <c r="E46">
-        <v>-187.316</v>
+        <v>-182.755</v>
       </c>
       <c r="F46">
-        <v>200.684</v>
+        <v>205.245</v>
       </c>
       <c r="G46">
         <v>88.59999999999999</v>
@@ -5428,45 +5428,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M46">
-        <v>11.5995352</v>
+        <v>12.5815185</v>
       </c>
       <c r="N46">
-        <v>35.26713146666668</v>
+        <v>34.28514816666667</v>
       </c>
       <c r="O46">
-        <v>11.99082469866667</v>
+        <v>11.65695037666667</v>
       </c>
       <c r="P46">
-        <v>23.276306768</v>
+        <v>22.62819779</v>
       </c>
       <c r="Q46">
-        <v>31.57630676800001</v>
+        <v>30.92819779</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1568377103554039</v>
+        <v>0.1584045642174275</v>
       </c>
       <c r="T46">
-        <v>1.447193597809673</v>
+        <v>1.467614956198332</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.34</v>
       </c>
       <c r="W46">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.040391779376356</v>
+        <v>3.725040555849175</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5474,22 +5474,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1053286103195851</v>
+        <v>0.105026582840144</v>
       </c>
       <c r="C47">
-        <v>241.2866968093466</v>
+        <v>238.5509786847364</v>
       </c>
       <c r="D47">
-        <v>357.9316968093466</v>
+        <v>359.7569786847365</v>
       </c>
       <c r="E47">
-        <v>-182.755</v>
+        <v>-178.194</v>
       </c>
       <c r="F47">
-        <v>205.245</v>
+        <v>209.806</v>
       </c>
       <c r="G47">
         <v>88.59999999999999</v>
@@ -5510,28 +5510,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M47">
-        <v>12.5815185</v>
+        <v>12.8611078</v>
       </c>
       <c r="N47">
-        <v>34.28514816666667</v>
+        <v>34.00555886666668</v>
       </c>
       <c r="O47">
-        <v>11.65695037666667</v>
+        <v>11.56189001466667</v>
       </c>
       <c r="P47">
-        <v>22.62819779</v>
+        <v>22.44366885200001</v>
       </c>
       <c r="Q47">
-        <v>30.92819779</v>
+        <v>30.74366885200001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1584045642174275</v>
+        <v>0.1600294497039704</v>
       </c>
       <c r="T47">
-        <v>1.467614956198332</v>
+        <v>1.488792661193979</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.725040555849175</v>
+        <v>3.644061413330714</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5556,22 +5556,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.105026582840144</v>
+        <v>0.104724555360703</v>
       </c>
       <c r="C48">
-        <v>238.5509786847364</v>
+        <v>235.8339721237765</v>
       </c>
       <c r="D48">
-        <v>359.7569786847365</v>
+        <v>361.6009721237766</v>
       </c>
       <c r="E48">
-        <v>-178.194</v>
+        <v>-173.633</v>
       </c>
       <c r="F48">
-        <v>209.806</v>
+        <v>214.367</v>
       </c>
       <c r="G48">
         <v>88.59999999999999</v>
@@ -5592,28 +5592,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M48">
-        <v>12.8611078</v>
+        <v>13.1406971</v>
       </c>
       <c r="N48">
-        <v>34.00555886666668</v>
+        <v>33.72596956666668</v>
       </c>
       <c r="O48">
-        <v>11.56189001466667</v>
+        <v>11.46682965266667</v>
       </c>
       <c r="P48">
-        <v>22.44366885200001</v>
+        <v>22.25913991400001</v>
       </c>
       <c r="Q48">
-        <v>30.74366885200001</v>
+        <v>30.55913991400001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1600294497039704</v>
+        <v>0.1617156516239678</v>
       </c>
       <c r="T48">
-        <v>1.488792661193979</v>
+        <v>1.510769524868707</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.644061413330714</v>
+        <v>3.566528191770487</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5638,22 +5638,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.104724555360703</v>
+        <v>0.1053095678812619</v>
       </c>
       <c r="C49">
-        <v>235.8339721237765</v>
+        <v>227.7182312027741</v>
       </c>
       <c r="D49">
-        <v>361.6009721237766</v>
+        <v>358.0462312027742</v>
       </c>
       <c r="E49">
-        <v>-173.633</v>
+        <v>-169.072</v>
       </c>
       <c r="F49">
-        <v>214.367</v>
+        <v>218.928</v>
       </c>
       <c r="G49">
         <v>88.59999999999999</v>
@@ -5674,45 +5674,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M49">
-        <v>13.1406971</v>
+        <v>14.0332848</v>
       </c>
       <c r="N49">
-        <v>33.72596956666668</v>
+        <v>32.83338186666667</v>
       </c>
       <c r="O49">
-        <v>11.46682965266667</v>
+        <v>11.16334983466667</v>
       </c>
       <c r="P49">
-        <v>22.25913991400001</v>
+        <v>21.670032032</v>
       </c>
       <c r="Q49">
-        <v>30.55913991400001</v>
+        <v>29.970032032</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1617156516239678</v>
+        <v>0.1634667074639652</v>
       </c>
       <c r="T49">
-        <v>1.510769524868707</v>
+        <v>1.533591652530925</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.34</v>
       </c>
       <c r="W49">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.566528191770487</v>
+        <v>3.339679008486072</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5720,22 +5720,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1053095678812619</v>
+        <v>0.1050260204018208</v>
       </c>
       <c r="C50">
-        <v>227.7182312027742</v>
+        <v>224.8713951072901</v>
       </c>
       <c r="D50">
-        <v>358.0462312027742</v>
+        <v>359.7603951072901</v>
       </c>
       <c r="E50">
-        <v>-169.072</v>
+        <v>-164.511</v>
       </c>
       <c r="F50">
-        <v>218.928</v>
+        <v>223.489</v>
       </c>
       <c r="G50">
         <v>88.59999999999999</v>
@@ -5756,28 +5756,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M50">
-        <v>14.0332848</v>
+        <v>14.3256449</v>
       </c>
       <c r="N50">
-        <v>32.83338186666667</v>
+        <v>32.54102176666667</v>
       </c>
       <c r="O50">
-        <v>11.16334983466667</v>
+        <v>11.06394740066667</v>
       </c>
       <c r="P50">
-        <v>21.670032032</v>
+        <v>21.477074366</v>
       </c>
       <c r="Q50">
-        <v>29.970032032</v>
+        <v>29.777074366</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1634667074639652</v>
+        <v>0.165286432160433</v>
       </c>
       <c r="T50">
-        <v>1.533591652530925</v>
+        <v>1.557308765591661</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.339679008486072</v>
+        <v>3.271522294027173</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5802,22 +5802,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1050260204018208</v>
+        <v>0.1047424729223797</v>
       </c>
       <c r="C51">
-        <v>224.8713951072901</v>
+        <v>222.0410512568841</v>
       </c>
       <c r="D51">
-        <v>359.7603951072901</v>
+        <v>361.4910512568842</v>
       </c>
       <c r="E51">
-        <v>-164.511</v>
+        <v>-159.95</v>
       </c>
       <c r="F51">
-        <v>223.489</v>
+        <v>228.05</v>
       </c>
       <c r="G51">
         <v>88.59999999999999</v>
@@ -5838,28 +5838,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M51">
-        <v>14.3256449</v>
+        <v>14.618005</v>
       </c>
       <c r="N51">
-        <v>32.54102176666667</v>
+        <v>32.24866166666667</v>
       </c>
       <c r="O51">
-        <v>11.06394740066667</v>
+        <v>10.96454496666667</v>
       </c>
       <c r="P51">
-        <v>21.477074366</v>
+        <v>21.2841167</v>
       </c>
       <c r="Q51">
-        <v>29.777074366</v>
+        <v>29.5841167</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.165286432160433</v>
+        <v>0.1671789458447595</v>
       </c>
       <c r="T51">
-        <v>1.557308765591661</v>
+        <v>1.581974563174826</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.271522294027173</v>
+        <v>3.206091848146629</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5884,22 +5884,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1047424729223797</v>
+        <v>0.1044589254429387</v>
       </c>
       <c r="C52">
-        <v>222.0410512568841</v>
+        <v>219.2274388138571</v>
       </c>
       <c r="D52">
-        <v>361.4910512568842</v>
+        <v>363.2384388138572</v>
       </c>
       <c r="E52">
-        <v>-159.95</v>
+        <v>-155.389</v>
       </c>
       <c r="F52">
-        <v>228.05</v>
+        <v>232.611</v>
       </c>
       <c r="G52">
         <v>88.59999999999999</v>
@@ -5920,28 +5920,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M52">
-        <v>14.618005</v>
+        <v>14.9103651</v>
       </c>
       <c r="N52">
-        <v>32.24866166666667</v>
+        <v>31.95630156666667</v>
       </c>
       <c r="O52">
-        <v>10.96454496666667</v>
+        <v>10.86514253266667</v>
       </c>
       <c r="P52">
-        <v>21.2841167</v>
+        <v>21.091159034</v>
       </c>
       <c r="Q52">
-        <v>29.5841167</v>
+        <v>29.391159034</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1671789458447595</v>
+        <v>0.1691487049855891</v>
       </c>
       <c r="T52">
-        <v>1.581974563174826</v>
+        <v>1.607647128006284</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.206091848146629</v>
+        <v>3.143227302104539</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5966,22 +5966,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1044589254429387</v>
+        <v>0.1041753779634976</v>
       </c>
       <c r="C53">
-        <v>219.2274388138571</v>
+        <v>216.4308015872542</v>
       </c>
       <c r="D53">
-        <v>363.2384388138572</v>
+        <v>365.0028015872543</v>
       </c>
       <c r="E53">
-        <v>-155.389</v>
+        <v>-150.828</v>
       </c>
       <c r="F53">
-        <v>232.611</v>
+        <v>237.172</v>
       </c>
       <c r="G53">
         <v>88.59999999999999</v>
@@ -6002,28 +6002,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M53">
-        <v>14.9103651</v>
+        <v>15.2027252</v>
       </c>
       <c r="N53">
-        <v>31.95630156666667</v>
+        <v>31.66394146666667</v>
       </c>
       <c r="O53">
-        <v>10.86514253266667</v>
+        <v>10.76574009866667</v>
       </c>
       <c r="P53">
-        <v>21.091159034</v>
+        <v>20.898201368</v>
       </c>
       <c r="Q53">
-        <v>29.391159034</v>
+        <v>29.198201368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1691487049855891</v>
+        <v>0.1712005374239533</v>
       </c>
       <c r="T53">
-        <v>1.607647128006284</v>
+        <v>1.634389383039052</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.143227302104539</v>
+        <v>3.082780623217912</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6048,22 +6048,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1041753779634976</v>
+        <v>0.1038918304840565</v>
       </c>
       <c r="C54">
-        <v>216.4308015872542</v>
+        <v>213.6513881462696</v>
       </c>
       <c r="D54">
-        <v>365.0028015872543</v>
+        <v>366.7843881462696</v>
       </c>
       <c r="E54">
-        <v>-150.828</v>
+        <v>-146.267</v>
       </c>
       <c r="F54">
-        <v>237.172</v>
+        <v>241.733</v>
       </c>
       <c r="G54">
         <v>88.59999999999999</v>
@@ -6084,28 +6084,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M54">
-        <v>15.2027252</v>
+        <v>15.4950853</v>
       </c>
       <c r="N54">
-        <v>31.66394146666667</v>
+        <v>31.37158136666667</v>
       </c>
       <c r="O54">
-        <v>10.76574009866667</v>
+        <v>10.66633766466667</v>
       </c>
       <c r="P54">
-        <v>20.898201368</v>
+        <v>20.705243702</v>
       </c>
       <c r="Q54">
-        <v>29.198201368</v>
+        <v>29.005243702</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1712005374239533</v>
+        <v>0.1733396818809713</v>
       </c>
       <c r="T54">
-        <v>1.634389383039052</v>
+        <v>1.662269606371087</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.082780623217912</v>
+        <v>3.024614951081726</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6130,22 +6130,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1038918304840565</v>
+        <v>0.1063882030046155</v>
       </c>
       <c r="C55">
-        <v>213.6513881462696</v>
+        <v>193.9780325699105</v>
       </c>
       <c r="D55">
-        <v>366.7843881462696</v>
+        <v>351.6720325699105</v>
       </c>
       <c r="E55">
-        <v>-146.267</v>
+        <v>-141.706</v>
       </c>
       <c r="F55">
-        <v>241.733</v>
+        <v>246.294</v>
       </c>
       <c r="G55">
         <v>88.59999999999999</v>
@@ -6166,45 +6166,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M55">
-        <v>15.4950853</v>
+        <v>17.7085386</v>
       </c>
       <c r="N55">
-        <v>31.37158136666667</v>
+        <v>29.15812806666667</v>
       </c>
       <c r="O55">
-        <v>10.66633766466667</v>
+        <v>9.913763542666668</v>
       </c>
       <c r="P55">
-        <v>20.705243702</v>
+        <v>19.244364524</v>
       </c>
       <c r="Q55">
-        <v>29.005243702</v>
+        <v>27.544364524</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1733396818809713</v>
+        <v>0.1755718326187292</v>
       </c>
       <c r="T55">
-        <v>1.662269606371087</v>
+        <v>1.691362013326255</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.34</v>
       </c>
       <c r="W55">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.024614951081726</v>
+        <v>2.646557557644348</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6212,22 +6212,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1063882030046155</v>
+        <v>0.1061561355251744</v>
       </c>
       <c r="C56">
-        <v>193.9780325699105</v>
+        <v>190.7692006880032</v>
       </c>
       <c r="D56">
-        <v>351.6720325699105</v>
+        <v>353.0242006880033</v>
       </c>
       <c r="E56">
-        <v>-141.706</v>
+        <v>-137.145</v>
       </c>
       <c r="F56">
-        <v>246.294</v>
+        <v>250.855</v>
       </c>
       <c r="G56">
         <v>88.59999999999999</v>
@@ -6248,28 +6248,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M56">
-        <v>17.7085386</v>
+        <v>18.0364745</v>
       </c>
       <c r="N56">
-        <v>29.15812806666667</v>
+        <v>28.83019216666667</v>
       </c>
       <c r="O56">
-        <v>9.913763542666668</v>
+        <v>9.802265336666668</v>
       </c>
       <c r="P56">
-        <v>19.244364524</v>
+        <v>19.02792683</v>
       </c>
       <c r="Q56">
-        <v>27.544364524</v>
+        <v>27.32792683</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1755718326187292</v>
+        <v>0.177903190055943</v>
       </c>
       <c r="T56">
-        <v>1.691362013326255</v>
+        <v>1.721747416146096</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.646557557644348</v>
+        <v>2.598438329323542</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6294,22 +6294,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1061561355251744</v>
+        <v>0.1059240680457333</v>
       </c>
       <c r="C57">
-        <v>190.7692006880032</v>
+        <v>187.5708070301597</v>
       </c>
       <c r="D57">
-        <v>353.0242006880033</v>
+        <v>354.3868070301598</v>
       </c>
       <c r="E57">
-        <v>-137.145</v>
+        <v>-132.584</v>
       </c>
       <c r="F57">
-        <v>250.855</v>
+        <v>255.416</v>
       </c>
       <c r="G57">
         <v>88.59999999999999</v>
@@ -6330,28 +6330,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M57">
-        <v>18.0364745</v>
+        <v>18.3644104</v>
       </c>
       <c r="N57">
-        <v>28.83019216666667</v>
+        <v>28.50225626666667</v>
       </c>
       <c r="O57">
-        <v>9.802265336666668</v>
+        <v>9.690767130666668</v>
       </c>
       <c r="P57">
-        <v>19.02792683</v>
+        <v>18.811489136</v>
       </c>
       <c r="Q57">
-        <v>27.32792683</v>
+        <v>27.111489136</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.177903190055943</v>
+        <v>0.1803405182857575</v>
       </c>
       <c r="T57">
-        <v>1.721747416146096</v>
+        <v>1.753513973639566</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.598438329323542</v>
+        <v>2.552037644871336</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6376,22 +6376,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1059240680457333</v>
+        <v>0.1056920005662922</v>
       </c>
       <c r="C58">
-        <v>187.5708070301597</v>
+        <v>184.382972933403</v>
       </c>
       <c r="D58">
-        <v>354.3868070301598</v>
+        <v>355.759972933403</v>
       </c>
       <c r="E58">
-        <v>-132.584</v>
+        <v>-128.023</v>
       </c>
       <c r="F58">
-        <v>255.416</v>
+        <v>259.977</v>
       </c>
       <c r="G58">
         <v>88.59999999999999</v>
@@ -6412,28 +6412,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M58">
-        <v>18.3644104</v>
+        <v>18.6923463</v>
       </c>
       <c r="N58">
-        <v>28.50225626666667</v>
+        <v>28.17432036666667</v>
       </c>
       <c r="O58">
-        <v>9.690767130666668</v>
+        <v>9.579268924666669</v>
       </c>
       <c r="P58">
-        <v>18.811489136</v>
+        <v>18.595051442</v>
       </c>
       <c r="Q58">
-        <v>27.111489136</v>
+        <v>26.895051442</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1803405182857575</v>
+        <v>0.1828912106192843</v>
       </c>
       <c r="T58">
-        <v>1.753513973639566</v>
+        <v>1.786758045435058</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.552037644871336</v>
+        <v>2.507265054610435</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6458,22 +6458,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1056920005662922</v>
+        <v>0.1069528530868511</v>
       </c>
       <c r="C59">
-        <v>184.382972933403</v>
+        <v>172.4868963843172</v>
       </c>
       <c r="D59">
-        <v>355.759972933403</v>
+        <v>348.4248963843172</v>
       </c>
       <c r="E59">
-        <v>-128.023</v>
+        <v>-123.4619999999999</v>
       </c>
       <c r="F59">
-        <v>259.977</v>
+        <v>264.5380000000001</v>
       </c>
       <c r="G59">
         <v>88.59999999999999</v>
@@ -6494,45 +6494,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M59">
-        <v>18.6923463</v>
+        <v>20.05198040000001</v>
       </c>
       <c r="N59">
-        <v>28.17432036666667</v>
+        <v>26.81468626666667</v>
       </c>
       <c r="O59">
-        <v>9.579268924666669</v>
+        <v>9.116993330666668</v>
       </c>
       <c r="P59">
-        <v>18.595051442</v>
+        <v>17.697692936</v>
       </c>
       <c r="Q59">
-        <v>26.895051442</v>
+        <v>25.997692936</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1828912106192843</v>
+        <v>0.1855633644925027</v>
       </c>
       <c r="T59">
-        <v>1.786758045435058</v>
+        <v>1.821585168268431</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.34</v>
       </c>
       <c r="W59">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.507265054610435</v>
+        <v>2.337258751094065</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6540,22 +6540,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1069528530868512</v>
+        <v>0.1067465256074101</v>
       </c>
       <c r="C60">
-        <v>172.4868963843171</v>
+        <v>169.1054489499314</v>
       </c>
       <c r="D60">
-        <v>348.4248963843172</v>
+        <v>349.6044489499313</v>
       </c>
       <c r="E60">
-        <v>-123.462</v>
+        <v>-118.901</v>
       </c>
       <c r="F60">
-        <v>264.538</v>
+        <v>269.099</v>
       </c>
       <c r="G60">
         <v>88.59999999999999</v>
@@ -6576,28 +6576,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M60">
-        <v>20.0519804</v>
+        <v>20.3977042</v>
       </c>
       <c r="N60">
-        <v>26.81468626666667</v>
+        <v>26.46896246666667</v>
       </c>
       <c r="O60">
-        <v>9.11699333066667</v>
+        <v>8.99944723866667</v>
       </c>
       <c r="P60">
-        <v>17.697692936</v>
+        <v>17.46951522800001</v>
       </c>
       <c r="Q60">
-        <v>25.997692936</v>
+        <v>25.76951522800001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1855633644925027</v>
+        <v>0.1883658673351465</v>
       </c>
       <c r="T60">
-        <v>1.821585168268431</v>
+        <v>1.858111175142456</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.337258751094065</v>
+        <v>2.297644195990776</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6622,22 +6622,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1067465256074101</v>
+        <v>0.106540198127969</v>
       </c>
       <c r="C61">
-        <v>169.1054489499314</v>
+        <v>165.7320151248268</v>
       </c>
       <c r="D61">
-        <v>349.6044489499313</v>
+        <v>350.7920151248268</v>
       </c>
       <c r="E61">
-        <v>-118.901</v>
+        <v>-114.34</v>
       </c>
       <c r="F61">
-        <v>269.099</v>
+        <v>273.66</v>
       </c>
       <c r="G61">
         <v>88.59999999999999</v>
@@ -6658,28 +6658,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M61">
-        <v>20.3977042</v>
+        <v>20.74342800000001</v>
       </c>
       <c r="N61">
-        <v>26.46896246666667</v>
+        <v>26.12323866666667</v>
       </c>
       <c r="O61">
-        <v>8.99944723866667</v>
+        <v>8.881901146666667</v>
       </c>
       <c r="P61">
-        <v>17.46951522800001</v>
+        <v>17.24133752</v>
       </c>
       <c r="Q61">
-        <v>25.76951522800001</v>
+        <v>25.54133752</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1883658673351465</v>
+        <v>0.1913084953199225</v>
       </c>
       <c r="T61">
-        <v>1.858111175142456</v>
+        <v>1.896463482360183</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.297644195990776</v>
+        <v>2.259350126057596</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6704,22 +6704,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.106540198127969</v>
+        <v>0.1063338706485279</v>
       </c>
       <c r="C62">
-        <v>165.7320151248268</v>
+        <v>162.3666768512841</v>
       </c>
       <c r="D62">
-        <v>350.7920151248268</v>
+        <v>351.987676851284</v>
       </c>
       <c r="E62">
-        <v>-114.34</v>
+        <v>-109.779</v>
       </c>
       <c r="F62">
-        <v>273.66</v>
+        <v>278.221</v>
       </c>
       <c r="G62">
         <v>88.59999999999999</v>
@@ -6740,28 +6740,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M62">
-        <v>20.74342800000001</v>
+        <v>21.0891518</v>
       </c>
       <c r="N62">
-        <v>26.12323866666667</v>
+        <v>25.77751486666667</v>
       </c>
       <c r="O62">
-        <v>8.881901146666667</v>
+        <v>8.76435505466667</v>
       </c>
       <c r="P62">
-        <v>17.24133752</v>
+        <v>17.013159812</v>
       </c>
       <c r="Q62">
-        <v>25.54133752</v>
+        <v>25.313159812</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1913084953199225</v>
+        <v>0.1944020273039178</v>
       </c>
       <c r="T62">
-        <v>1.896463482360183</v>
+        <v>1.936782574563434</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.259350126057596</v>
+        <v>2.222311599400914</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6786,22 +6786,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1063338706485279</v>
+        <v>0.1061275431690868</v>
       </c>
       <c r="C63">
-        <v>162.3666768512841</v>
+        <v>159.0095171925938</v>
       </c>
       <c r="D63">
-        <v>351.987676851284</v>
+        <v>353.1915171925938</v>
       </c>
       <c r="E63">
-        <v>-109.779</v>
+        <v>-105.218</v>
       </c>
       <c r="F63">
-        <v>278.221</v>
+        <v>282.782</v>
       </c>
       <c r="G63">
         <v>88.59999999999999</v>
@@ -6822,28 +6822,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M63">
-        <v>21.0891518</v>
+        <v>21.43487560000001</v>
       </c>
       <c r="N63">
-        <v>25.77751486666667</v>
+        <v>25.43179106666667</v>
       </c>
       <c r="O63">
-        <v>8.76435505466667</v>
+        <v>8.646808962666668</v>
       </c>
       <c r="P63">
-        <v>17.013159812</v>
+        <v>16.784982104</v>
       </c>
       <c r="Q63">
-        <v>25.313159812</v>
+        <v>25.084982104</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1944020273039178</v>
+        <v>0.1976583767607549</v>
       </c>
       <c r="T63">
-        <v>1.936782574563434</v>
+        <v>1.979223724251066</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.222311599400914</v>
+        <v>2.186467863926706</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6868,22 +6868,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1061275431690868</v>
+        <v>0.1059212156896458</v>
       </c>
       <c r="C64">
-        <v>159.0095171925938</v>
+        <v>155.6606203522919</v>
       </c>
       <c r="D64">
-        <v>353.1915171925938</v>
+        <v>354.403620352292</v>
       </c>
       <c r="E64">
-        <v>-105.218</v>
+        <v>-100.657</v>
       </c>
       <c r="F64">
-        <v>282.782</v>
+        <v>287.343</v>
       </c>
       <c r="G64">
         <v>88.59999999999999</v>
@@ -6904,28 +6904,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M64">
-        <v>21.43487560000001</v>
+        <v>21.7805994</v>
       </c>
       <c r="N64">
-        <v>25.43179106666667</v>
+        <v>25.08606726666667</v>
       </c>
       <c r="O64">
-        <v>8.646808962666668</v>
+        <v>8.529262870666669</v>
       </c>
       <c r="P64">
-        <v>16.784982104</v>
+        <v>16.556804396</v>
       </c>
       <c r="Q64">
-        <v>25.084982104</v>
+        <v>24.856804396</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1976583767607549</v>
+        <v>0.2010907451071507</v>
       </c>
       <c r="T64">
-        <v>1.979223724251066</v>
+        <v>2.02395899013803</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.186467863926706</v>
+        <v>2.151762024816758</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6950,22 +6950,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1059212156896458</v>
+        <v>0.1057148882102047</v>
       </c>
       <c r="C65">
-        <v>155.6606203522919</v>
+        <v>152.3200716937937</v>
       </c>
       <c r="D65">
-        <v>354.403620352292</v>
+        <v>355.6240716937937</v>
       </c>
       <c r="E65">
-        <v>-100.657</v>
+        <v>-96.096</v>
       </c>
       <c r="F65">
-        <v>287.343</v>
+        <v>291.904</v>
       </c>
       <c r="G65">
         <v>88.59999999999999</v>
@@ -6986,28 +6986,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M65">
-        <v>21.7805994</v>
+        <v>22.1263232</v>
       </c>
       <c r="N65">
-        <v>25.08606726666667</v>
+        <v>24.74034346666667</v>
       </c>
       <c r="O65">
-        <v>8.529262870666669</v>
+        <v>8.411716778666669</v>
       </c>
       <c r="P65">
-        <v>16.556804396</v>
+        <v>16.328626688</v>
       </c>
       <c r="Q65">
-        <v>24.856804396</v>
+        <v>24.628626688</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2010907451071507</v>
+        <v>0.204713800583902</v>
       </c>
       <c r="T65">
-        <v>2.02395899013803</v>
+        <v>2.07117954857427</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.151762024816758</v>
+        <v>2.118140743178996</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7032,22 +7032,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1057148882102047</v>
+        <v>0.1055085607307636</v>
       </c>
       <c r="C66">
-        <v>152.3200716937937</v>
+        <v>148.9879577604335</v>
       </c>
       <c r="D66">
-        <v>355.6240716937937</v>
+        <v>356.8529577604335</v>
       </c>
       <c r="E66">
-        <v>-96.096</v>
+        <v>-91.53499999999997</v>
       </c>
       <c r="F66">
-        <v>291.904</v>
+        <v>296.465</v>
       </c>
       <c r="G66">
         <v>88.59999999999999</v>
@@ -7068,28 +7068,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M66">
-        <v>22.1263232</v>
+        <v>22.472047</v>
       </c>
       <c r="N66">
-        <v>24.74034346666667</v>
+        <v>24.39461966666667</v>
       </c>
       <c r="O66">
-        <v>8.411716778666669</v>
+        <v>8.294170686666668</v>
       </c>
       <c r="P66">
-        <v>16.328626688</v>
+        <v>16.10044898</v>
       </c>
       <c r="Q66">
-        <v>24.628626688</v>
+        <v>24.40044898</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.204713800583902</v>
+        <v>0.2085438878021819</v>
       </c>
       <c r="T66">
-        <v>2.07117954857427</v>
+        <v>2.121098424635438</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.118140743178996</v>
+        <v>2.085553962514704</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7114,22 +7114,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1055085607307636</v>
+        <v>0.1053022332513225</v>
       </c>
       <c r="C67">
-        <v>148.9879577604335</v>
+        <v>145.664366295922</v>
       </c>
       <c r="D67">
-        <v>356.8529577604335</v>
+        <v>358.090366295922</v>
       </c>
       <c r="E67">
-        <v>-91.53499999999997</v>
+        <v>-86.97399999999999</v>
       </c>
       <c r="F67">
-        <v>296.465</v>
+        <v>301.026</v>
       </c>
       <c r="G67">
         <v>88.59999999999999</v>
@@ -7150,28 +7150,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M67">
-        <v>22.472047</v>
+        <v>22.8177708</v>
       </c>
       <c r="N67">
-        <v>24.39461966666667</v>
+        <v>24.04889586666667</v>
       </c>
       <c r="O67">
-        <v>8.294170686666668</v>
+        <v>8.17662459466667</v>
       </c>
       <c r="P67">
-        <v>16.10044898</v>
+        <v>15.872271272</v>
       </c>
       <c r="Q67">
-        <v>24.40044898</v>
+        <v>24.172271272</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2085438878021819</v>
+        <v>0.2125992742685958</v>
       </c>
       <c r="T67">
-        <v>2.121098424635438</v>
+        <v>2.173953705170792</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.085553962514704</v>
+        <v>2.05395466005236</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7196,22 +7196,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1053022332513225</v>
+        <v>0.1050959057718815</v>
       </c>
       <c r="C68">
-        <v>145.664366295922</v>
+        <v>142.34938626523</v>
       </c>
       <c r="D68">
-        <v>358.090366295922</v>
+        <v>359.33638626523</v>
       </c>
       <c r="E68">
-        <v>-86.97399999999999</v>
+        <v>-82.41299999999995</v>
       </c>
       <c r="F68">
-        <v>301.026</v>
+        <v>305.587</v>
       </c>
       <c r="G68">
         <v>88.59999999999999</v>
@@ -7232,28 +7232,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M68">
-        <v>22.8177708</v>
+        <v>23.16349460000001</v>
       </c>
       <c r="N68">
-        <v>24.04889586666667</v>
+        <v>23.70317206666667</v>
       </c>
       <c r="O68">
-        <v>8.17662459466667</v>
+        <v>8.059078502666667</v>
       </c>
       <c r="P68">
-        <v>15.872271272</v>
+        <v>15.644093564</v>
       </c>
       <c r="Q68">
-        <v>24.172271272</v>
+        <v>23.944093564</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2125992742685958</v>
+        <v>0.2169004417329742</v>
       </c>
       <c r="T68">
-        <v>2.173953705170792</v>
+        <v>2.230012336041622</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.05395466005236</v>
+        <v>2.023298620350086</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7278,22 +7278,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1050959057718815</v>
+        <v>0.1112625382924404</v>
       </c>
       <c r="C69">
-        <v>142.34938626523</v>
+        <v>103.9385615690925</v>
       </c>
       <c r="D69">
-        <v>359.33638626523</v>
+        <v>325.4865615690925</v>
       </c>
       <c r="E69">
-        <v>-82.41299999999995</v>
+        <v>-77.85199999999998</v>
       </c>
       <c r="F69">
-        <v>305.587</v>
+        <v>310.148</v>
       </c>
       <c r="G69">
         <v>88.59999999999999</v>
@@ -7314,45 +7314,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M69">
-        <v>23.16349460000001</v>
+        <v>27.91332</v>
       </c>
       <c r="N69">
-        <v>23.70317206666667</v>
+        <v>18.95334666666667</v>
       </c>
       <c r="O69">
-        <v>8.059078502666667</v>
+        <v>6.444137866666669</v>
       </c>
       <c r="P69">
-        <v>15.644093564</v>
+        <v>12.5092088</v>
       </c>
       <c r="Q69">
-        <v>23.944093564</v>
+        <v>20.8092088</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2169004417329742</v>
+        <v>0.2214704321638763</v>
       </c>
       <c r="T69">
-        <v>2.230012336041622</v>
+        <v>2.289574631341879</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.34</v>
       </c>
       <c r="W69">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.023298620350086</v>
+        <v>1.679007250540841</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7360,22 +7360,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1112625382924404</v>
+        <v>0.1111499308129993</v>
       </c>
       <c r="C70">
-        <v>103.9385615690925</v>
+        <v>99.93842247336977</v>
       </c>
       <c r="D70">
-        <v>325.4865615690925</v>
+        <v>326.0474224733698</v>
       </c>
       <c r="E70">
-        <v>-77.85199999999998</v>
+        <v>-73.29099999999994</v>
       </c>
       <c r="F70">
-        <v>310.148</v>
+        <v>314.7090000000001</v>
       </c>
       <c r="G70">
         <v>88.59999999999999</v>
@@ -7396,28 +7396,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M70">
-        <v>27.91332</v>
+        <v>28.32381000000001</v>
       </c>
       <c r="N70">
-        <v>18.95334666666667</v>
+        <v>18.54285666666667</v>
       </c>
       <c r="O70">
-        <v>6.444137866666669</v>
+        <v>6.304571266666668</v>
       </c>
       <c r="P70">
-        <v>12.5092088</v>
+        <v>12.2382854</v>
       </c>
       <c r="Q70">
-        <v>20.8092088</v>
+        <v>20.5382854</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2214704321638763</v>
+        <v>0.2263352606870947</v>
       </c>
       <c r="T70">
-        <v>2.289574631341879</v>
+        <v>2.352979655371185</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.679007250540841</v>
+        <v>1.654673812127206</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7442,22 +7442,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1111499308129993</v>
+        <v>0.1110373233335582</v>
       </c>
       <c r="C71">
-        <v>99.93842247336977</v>
+        <v>95.94021960462641</v>
       </c>
       <c r="D71">
-        <v>326.0474224733698</v>
+        <v>326.6102196046264</v>
       </c>
       <c r="E71">
-        <v>-73.29099999999994</v>
+        <v>-68.72999999999996</v>
       </c>
       <c r="F71">
-        <v>314.7090000000001</v>
+        <v>319.27</v>
       </c>
       <c r="G71">
         <v>88.59999999999999</v>
@@ -7478,28 +7478,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M71">
-        <v>28.32381000000001</v>
+        <v>28.7343</v>
       </c>
       <c r="N71">
-        <v>18.54285666666667</v>
+        <v>18.13236666666667</v>
       </c>
       <c r="O71">
-        <v>6.304571266666668</v>
+        <v>6.165004666666669</v>
       </c>
       <c r="P71">
-        <v>12.2382854</v>
+        <v>11.967362</v>
       </c>
       <c r="Q71">
-        <v>20.5382854</v>
+        <v>20.26736200000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2263352606870947</v>
+        <v>0.2315244111118609</v>
       </c>
       <c r="T71">
-        <v>2.352979655371185</v>
+        <v>2.420611681002445</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.654673812127206</v>
+        <v>1.631035614811103</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7524,22 +7524,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1110373233335582</v>
+        <v>0.1109247158541172</v>
       </c>
       <c r="C72">
-        <v>95.94021960462641</v>
+        <v>91.94396300668217</v>
       </c>
       <c r="D72">
-        <v>326.6102196046264</v>
+        <v>327.1749630066823</v>
       </c>
       <c r="E72">
-        <v>-68.72999999999996</v>
+        <v>-64.16899999999993</v>
       </c>
       <c r="F72">
-        <v>319.27</v>
+        <v>323.8310000000001</v>
       </c>
       <c r="G72">
         <v>88.59999999999999</v>
@@ -7560,28 +7560,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M72">
-        <v>28.7343</v>
+        <v>29.14479</v>
       </c>
       <c r="N72">
-        <v>18.13236666666667</v>
+        <v>17.72187666666667</v>
       </c>
       <c r="O72">
-        <v>6.165004666666669</v>
+        <v>6.025438066666668</v>
       </c>
       <c r="P72">
-        <v>11.967362</v>
+        <v>11.6964386</v>
       </c>
       <c r="Q72">
-        <v>20.26736200000001</v>
+        <v>19.9964386</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2315244111118609</v>
+        <v>0.2370714339797145</v>
       </c>
       <c r="T72">
-        <v>2.420611681002445</v>
+        <v>2.492907984263447</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.631035614811103</v>
+        <v>1.608063282208129</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7606,22 +7606,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1109247158541172</v>
+        <v>0.1108121083746761</v>
       </c>
       <c r="C73">
-        <v>91.94396300668222</v>
+        <v>87.94966279294482</v>
       </c>
       <c r="D73">
-        <v>327.1749630066823</v>
+        <v>327.7416627929449</v>
       </c>
       <c r="E73">
-        <v>-64.16899999999998</v>
+        <v>-59.608</v>
       </c>
       <c r="F73">
-        <v>323.831</v>
+        <v>328.392</v>
       </c>
       <c r="G73">
         <v>88.59999999999999</v>
@@ -7642,28 +7642,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M73">
-        <v>29.14479</v>
+        <v>29.55528</v>
       </c>
       <c r="N73">
-        <v>17.72187666666667</v>
+        <v>17.31138666666667</v>
       </c>
       <c r="O73">
-        <v>6.02543806666667</v>
+        <v>5.88587146666667</v>
       </c>
       <c r="P73">
-        <v>11.6964386</v>
+        <v>11.4255152</v>
       </c>
       <c r="Q73">
-        <v>19.9964386</v>
+        <v>19.7255152</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2370714339797144</v>
+        <v>0.2430146727667004</v>
       </c>
       <c r="T73">
-        <v>2.492907984263446</v>
+        <v>2.570368309185947</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.60806328220813</v>
+        <v>1.585729069955239</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7688,22 +7688,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1108121083746761</v>
+        <v>0.110699500895235</v>
       </c>
       <c r="C74">
-        <v>87.94966279294482</v>
+        <v>83.95732914701301</v>
       </c>
       <c r="D74">
-        <v>327.7416627929449</v>
+        <v>328.310329147013</v>
       </c>
       <c r="E74">
-        <v>-59.608</v>
+        <v>-55.04699999999997</v>
       </c>
       <c r="F74">
-        <v>328.392</v>
+        <v>332.953</v>
       </c>
       <c r="G74">
         <v>88.59999999999999</v>
@@ -7724,28 +7724,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M74">
-        <v>29.55528</v>
+        <v>29.96577</v>
       </c>
       <c r="N74">
-        <v>17.31138666666667</v>
+        <v>16.90089666666667</v>
       </c>
       <c r="O74">
-        <v>5.88587146666667</v>
+        <v>5.746304866666669</v>
       </c>
       <c r="P74">
-        <v>11.4255152</v>
+        <v>11.1545918</v>
       </c>
       <c r="Q74">
-        <v>19.7255152</v>
+        <v>19.4545918</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2430146727667004</v>
+        <v>0.2493981514638335</v>
       </c>
       <c r="T74">
-        <v>2.570368309185947</v>
+        <v>2.653566435954561</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.585729069955239</v>
+        <v>1.564006753928455</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7770,22 +7770,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.110699500895235</v>
+        <v>0.1105868934157939</v>
       </c>
       <c r="C75">
-        <v>83.95732914701301</v>
+        <v>79.96697232328711</v>
       </c>
       <c r="D75">
-        <v>328.310329147013</v>
+        <v>328.8809723232871</v>
       </c>
       <c r="E75">
-        <v>-55.04699999999997</v>
+        <v>-50.48599999999999</v>
       </c>
       <c r="F75">
-        <v>332.953</v>
+        <v>337.514</v>
       </c>
       <c r="G75">
         <v>88.59999999999999</v>
@@ -7806,28 +7806,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M75">
-        <v>29.96577</v>
+        <v>30.37626</v>
       </c>
       <c r="N75">
-        <v>16.90089666666667</v>
+        <v>16.49040666666668</v>
       </c>
       <c r="O75">
-        <v>5.746304866666669</v>
+        <v>5.60673826666667</v>
       </c>
       <c r="P75">
-        <v>11.1545918</v>
+        <v>10.8836684</v>
       </c>
       <c r="Q75">
-        <v>19.4545918</v>
+        <v>19.18366840000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2493981514638335</v>
+        <v>0.2562726669838229</v>
       </c>
       <c r="T75">
-        <v>2.653566435954561</v>
+        <v>2.743164418628452</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.564006753928455</v>
+        <v>1.542871527524016</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7852,22 +7852,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1105868934157939</v>
+        <v>0.1104742859363529</v>
       </c>
       <c r="C76">
-        <v>79.96697232328711</v>
+        <v>75.97860264758469</v>
       </c>
       <c r="D76">
-        <v>328.8809723232871</v>
+        <v>329.4536026475848</v>
       </c>
       <c r="E76">
-        <v>-50.48599999999999</v>
+        <v>-45.92499999999995</v>
       </c>
       <c r="F76">
-        <v>337.514</v>
+        <v>342.075</v>
       </c>
       <c r="G76">
         <v>88.59999999999999</v>
@@ -7888,28 +7888,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M76">
-        <v>30.37626</v>
+        <v>30.78675</v>
       </c>
       <c r="N76">
-        <v>16.49040666666668</v>
+        <v>16.07991666666667</v>
       </c>
       <c r="O76">
-        <v>5.60673826666667</v>
+        <v>5.467171666666669</v>
       </c>
       <c r="P76">
-        <v>10.8836684</v>
+        <v>10.612745</v>
       </c>
       <c r="Q76">
-        <v>19.18366840000001</v>
+        <v>18.912745</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2562726669838229</v>
+        <v>0.2636971437454115</v>
       </c>
       <c r="T76">
-        <v>2.743164418628452</v>
+        <v>2.839930239916253</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.542871527524016</v>
+        <v>1.522299907157029</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7934,22 +7934,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1104742859363529</v>
+        <v>0.1103616784569118</v>
       </c>
       <c r="C77">
-        <v>75.97860264758469</v>
+        <v>71.99223051776443</v>
       </c>
       <c r="D77">
-        <v>329.4536026475848</v>
+        <v>330.0282305177645</v>
       </c>
       <c r="E77">
-        <v>-45.92499999999995</v>
+        <v>-41.36399999999998</v>
       </c>
       <c r="F77">
-        <v>342.075</v>
+        <v>346.636</v>
       </c>
       <c r="G77">
         <v>88.59999999999999</v>
@@ -7970,28 +7970,28 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M77">
-        <v>30.78675</v>
+        <v>31.19724</v>
       </c>
       <c r="N77">
-        <v>16.07991666666667</v>
+        <v>15.66942666666667</v>
       </c>
       <c r="O77">
-        <v>5.467171666666669</v>
+        <v>5.32760506666667</v>
       </c>
       <c r="P77">
-        <v>10.612745</v>
+        <v>10.3418216</v>
       </c>
       <c r="Q77">
-        <v>18.912745</v>
+        <v>18.6418216</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2636971437454115</v>
+        <v>0.2717403269037992</v>
       </c>
       <c r="T77">
-        <v>2.839930239916253</v>
+        <v>2.944759879644706</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.522299907157029</v>
+        <v>1.502269645220753</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8016,22 +8016,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1103616784569118</v>
+        <v>0.1443513459435454</v>
       </c>
       <c r="C78">
-        <v>71.99223051776443</v>
+        <v>-46.39318972837589</v>
       </c>
       <c r="D78">
-        <v>330.0282305177645</v>
+        <v>216.2038102716241</v>
       </c>
       <c r="E78">
-        <v>-41.36399999999998</v>
+        <v>-36.803</v>
       </c>
       <c r="F78">
-        <v>346.636</v>
+        <v>351.197</v>
       </c>
       <c r="G78">
         <v>88.59999999999999</v>
@@ -8052,45 +8052,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M78">
-        <v>31.19724</v>
+        <v>51.5557196</v>
       </c>
       <c r="N78">
-        <v>15.66942666666667</v>
+        <v>-4.689052933333329</v>
       </c>
       <c r="O78">
-        <v>5.32760506666667</v>
+        <v>-1.594277997333332</v>
       </c>
       <c r="P78">
-        <v>10.3418216</v>
+        <v>-3.094774935999997</v>
       </c>
       <c r="Q78">
-        <v>18.6418216</v>
+        <v>5.205225064000004</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2717403269037992</v>
+        <v>0.2880527339686922</v>
       </c>
       <c r="T78">
-        <v>2.944759879644706</v>
+        <v>3.157365227806313</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.34</v>
+        <v>0.3090766027571201</v>
       </c>
       <c r="W78">
-        <v>0.05939999999999999</v>
+        <v>0.1014275547152548</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.502269645220753</v>
+        <v>0.9090488316385884</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8098,22 +8098,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1443513459435454</v>
+        <v>0.1453613459435454</v>
       </c>
       <c r="C79">
-        <v>-46.39318972837589</v>
+        <v>-53.14746912114509</v>
       </c>
       <c r="D79">
-        <v>216.2038102716241</v>
+        <v>214.010530878855</v>
       </c>
       <c r="E79">
-        <v>-36.803</v>
+        <v>-32.24199999999996</v>
       </c>
       <c r="F79">
-        <v>351.197</v>
+        <v>355.758</v>
       </c>
       <c r="G79">
         <v>88.59999999999999</v>
@@ -8134,37 +8134,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M79">
-        <v>51.5557196</v>
+        <v>52.22527440000001</v>
       </c>
       <c r="N79">
-        <v>-4.689052933333329</v>
+        <v>-5.358607733333336</v>
       </c>
       <c r="O79">
-        <v>-1.594277997333332</v>
+        <v>-1.821926629333334</v>
       </c>
       <c r="P79">
-        <v>-3.094774935999997</v>
+        <v>-3.536681104000002</v>
       </c>
       <c r="Q79">
-        <v>5.205225064000004</v>
+        <v>4.763318895999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2880527339686922</v>
+        <v>0.29906422187636</v>
       </c>
       <c r="T79">
-        <v>3.157365227806313</v>
+        <v>3.300881829070236</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.3090766027571201</v>
+        <v>0.3051140822089518</v>
       </c>
       <c r="W79">
-        <v>0.1014275547152548</v>
+        <v>0.1020092527317259</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9090488316385884</v>
+        <v>0.8973943594380935</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8180,22 +8180,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1453613459435454</v>
+        <v>0.1463713459435454</v>
       </c>
       <c r="C80">
-        <v>-53.14746912114509</v>
+        <v>-59.85769596264504</v>
       </c>
       <c r="D80">
-        <v>214.010530878855</v>
+        <v>211.861304037355</v>
       </c>
       <c r="E80">
-        <v>-32.24199999999996</v>
+        <v>-27.68099999999998</v>
       </c>
       <c r="F80">
-        <v>355.758</v>
+        <v>360.319</v>
       </c>
       <c r="G80">
         <v>88.59999999999999</v>
@@ -8216,37 +8216,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M80">
-        <v>52.22527440000001</v>
+        <v>52.89482920000001</v>
       </c>
       <c r="N80">
-        <v>-5.358607733333336</v>
+        <v>-6.028162533333337</v>
       </c>
       <c r="O80">
-        <v>-1.821926629333334</v>
+        <v>-2.049575261333334</v>
       </c>
       <c r="P80">
-        <v>-3.536681104000002</v>
+        <v>-3.978587272000002</v>
       </c>
       <c r="Q80">
-        <v>4.763318895999999</v>
+        <v>4.321412727999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.29906422187636</v>
+        <v>0.3111244229180914</v>
       </c>
       <c r="T80">
-        <v>3.300881829070236</v>
+        <v>3.458066678073581</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.3051140822089518</v>
+        <v>0.3012518786366866</v>
       </c>
       <c r="W80">
-        <v>0.1020092527317259</v>
+        <v>0.1025762242161344</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8973943594380935</v>
+        <v>0.8860349371667253</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8262,22 +8262,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1463713459435454</v>
+        <v>0.1473813459435454</v>
       </c>
       <c r="C81">
-        <v>-59.85769596264504</v>
+        <v>-66.52518426608469</v>
       </c>
       <c r="D81">
-        <v>211.861304037355</v>
+        <v>209.7548157339154</v>
       </c>
       <c r="E81">
-        <v>-27.68099999999998</v>
+        <v>-23.11999999999995</v>
       </c>
       <c r="F81">
-        <v>360.319</v>
+        <v>364.8800000000001</v>
       </c>
       <c r="G81">
         <v>88.59999999999999</v>
@@ -8298,37 +8298,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M81">
-        <v>52.89482920000001</v>
+        <v>53.56438400000001</v>
       </c>
       <c r="N81">
-        <v>-6.028162533333337</v>
+        <v>-6.697717333333337</v>
       </c>
       <c r="O81">
-        <v>-2.049575261333334</v>
+        <v>-2.277223893333335</v>
       </c>
       <c r="P81">
-        <v>-3.978587272000002</v>
+        <v>-4.420493440000002</v>
       </c>
       <c r="Q81">
-        <v>4.321412727999999</v>
+        <v>3.879506559999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3111244229180914</v>
+        <v>0.324390644063996</v>
       </c>
       <c r="T81">
-        <v>3.458066678073581</v>
+        <v>3.63097001197726</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.3012518786366866</v>
+        <v>0.297486230153728</v>
       </c>
       <c r="W81">
-        <v>0.1025762242161344</v>
+        <v>0.1031290214134327</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8860349371667253</v>
+        <v>0.8749595004521412</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8344,22 +8344,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1473813459435454</v>
+        <v>0.1483913459435454</v>
       </c>
       <c r="C82">
-        <v>-66.52518426608469</v>
+        <v>-73.15119629943712</v>
       </c>
       <c r="D82">
-        <v>209.7548157339154</v>
+        <v>207.6898037005629</v>
       </c>
       <c r="E82">
-        <v>-23.11999999999995</v>
+        <v>-18.55899999999997</v>
       </c>
       <c r="F82">
-        <v>364.8800000000001</v>
+        <v>369.441</v>
       </c>
       <c r="G82">
         <v>88.59999999999999</v>
@@ -8380,37 +8380,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M82">
-        <v>53.56438400000001</v>
+        <v>54.23393880000001</v>
       </c>
       <c r="N82">
-        <v>-6.697717333333337</v>
+        <v>-7.367272133333337</v>
       </c>
       <c r="O82">
-        <v>-2.277223893333335</v>
+        <v>-2.504872525333335</v>
       </c>
       <c r="P82">
-        <v>-4.420493440000002</v>
+        <v>-4.862399608000002</v>
       </c>
       <c r="Q82">
-        <v>3.879506559999998</v>
+        <v>3.437600391999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.324390644063996</v>
+        <v>0.3390533095410485</v>
       </c>
       <c r="T82">
-        <v>3.63097001197726</v>
+        <v>3.822073696818169</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.297486230153728</v>
+        <v>0.2938135606456573</v>
       </c>
       <c r="W82">
-        <v>0.1031290214134327</v>
+        <v>0.1036681692972175</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8749595004521412</v>
+        <v>0.8641575313107568</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8426,22 +8426,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1483913459435454</v>
+        <v>0.1494013459435454</v>
       </c>
       <c r="C83">
-        <v>-73.15119629943712</v>
+        <v>-79.73694510773811</v>
       </c>
       <c r="D83">
-        <v>207.6898037005629</v>
+        <v>205.665054892262</v>
       </c>
       <c r="E83">
-        <v>-18.55899999999997</v>
+        <v>-13.99799999999993</v>
       </c>
       <c r="F83">
-        <v>369.441</v>
+        <v>374.0020000000001</v>
       </c>
       <c r="G83">
         <v>88.59999999999999</v>
@@ -8462,37 +8462,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M83">
-        <v>54.23393880000001</v>
+        <v>54.90349360000001</v>
       </c>
       <c r="N83">
-        <v>-7.367272133333337</v>
+        <v>-8.036826933333337</v>
       </c>
       <c r="O83">
-        <v>-2.504872525333335</v>
+        <v>-2.732521157333335</v>
       </c>
       <c r="P83">
-        <v>-4.862399608000002</v>
+        <v>-5.304305776000002</v>
       </c>
       <c r="Q83">
-        <v>3.437600391999998</v>
+        <v>2.995694223999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3390533095410485</v>
+        <v>0.3553451600711067</v>
       </c>
       <c r="T83">
-        <v>3.822073696818169</v>
+        <v>4.034411124419178</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2938135606456573</v>
+        <v>0.2902304684426615</v>
       </c>
       <c r="W83">
-        <v>0.1036681692972175</v>
+        <v>0.1041941672326173</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8641575313107568</v>
+        <v>0.8536190248313573</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8508,22 +8508,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1494013459435454</v>
+        <v>0.1504113459435454</v>
       </c>
       <c r="C84">
-        <v>-79.73694510773811</v>
+        <v>-86.2835968892694</v>
       </c>
       <c r="D84">
-        <v>205.665054892262</v>
+        <v>203.6794031107307</v>
       </c>
       <c r="E84">
-        <v>-13.99799999999993</v>
+        <v>-9.436999999999955</v>
       </c>
       <c r="F84">
-        <v>374.0020000000001</v>
+        <v>378.563</v>
       </c>
       <c r="G84">
         <v>88.59999999999999</v>
@@ -8544,37 +8544,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M84">
-        <v>54.90349360000001</v>
+        <v>55.57304840000001</v>
       </c>
       <c r="N84">
-        <v>-8.036826933333337</v>
+        <v>-8.706381733333338</v>
       </c>
       <c r="O84">
-        <v>-2.732521157333335</v>
+        <v>-2.960169789333335</v>
       </c>
       <c r="P84">
-        <v>-5.304305776000002</v>
+        <v>-5.746211944000002</v>
       </c>
       <c r="Q84">
-        <v>2.995694223999998</v>
+        <v>2.553788055999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3553451600711067</v>
+        <v>0.3735536988988189</v>
       </c>
       <c r="T84">
-        <v>4.034411124419178</v>
+        <v>4.271729425855601</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2902304684426615</v>
+        <v>0.2867337158108222</v>
       </c>
       <c r="W84">
-        <v>0.1041941672326173</v>
+        <v>0.1047074905189713</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8536190248313573</v>
+        <v>0.8433344582671241</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8590,22 +8590,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1504113459435454</v>
+        <v>0.1514213459435454</v>
       </c>
       <c r="C85">
-        <v>-86.2835968892694</v>
+        <v>-92.79227323541062</v>
       </c>
       <c r="D85">
-        <v>203.6794031107307</v>
+        <v>201.7317267645895</v>
       </c>
       <c r="E85">
-        <v>-9.436999999999955</v>
+        <v>-4.87599999999992</v>
       </c>
       <c r="F85">
-        <v>378.563</v>
+        <v>383.1240000000001</v>
       </c>
       <c r="G85">
         <v>88.59999999999999</v>
@@ -8626,37 +8626,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M85">
-        <v>55.57304840000001</v>
+        <v>56.24260320000002</v>
       </c>
       <c r="N85">
-        <v>-8.706381733333338</v>
+        <v>-9.375936533333345</v>
       </c>
       <c r="O85">
-        <v>-2.960169789333335</v>
+        <v>-3.187818421333338</v>
       </c>
       <c r="P85">
-        <v>-5.746211944000002</v>
+        <v>-6.188118112000007</v>
       </c>
       <c r="Q85">
-        <v>2.553788055999998</v>
+        <v>2.111881887999994</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3735536988988189</v>
+        <v>0.3940383050799952</v>
       </c>
       <c r="T85">
-        <v>4.271729425855601</v>
+        <v>4.538712514971577</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2867337158108222</v>
+        <v>0.2833202191940267</v>
       </c>
       <c r="W85">
-        <v>0.1047074905189713</v>
+        <v>0.1052085918223169</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8433344582671241</v>
+        <v>0.8332947623353725</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8672,22 +8672,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1514213459435454</v>
+        <v>0.1524313459435454</v>
       </c>
       <c r="C86">
-        <v>-92.79227323541056</v>
+        <v>-99.26405324319654</v>
       </c>
       <c r="D86">
-        <v>201.7317267645895</v>
+        <v>199.8209467568035</v>
       </c>
       <c r="E86">
-        <v>-4.875999999999976</v>
+        <v>-0.3149999999999977</v>
       </c>
       <c r="F86">
-        <v>383.124</v>
+        <v>387.685</v>
       </c>
       <c r="G86">
         <v>88.59999999999999</v>
@@ -8708,37 +8708,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M86">
-        <v>56.24260320000001</v>
+        <v>56.91215800000001</v>
       </c>
       <c r="N86">
-        <v>-9.375936533333338</v>
+        <v>-10.04549133333333</v>
       </c>
       <c r="O86">
-        <v>-3.187818421333335</v>
+        <v>-3.415467053333333</v>
       </c>
       <c r="P86">
-        <v>-6.188118112000003</v>
+        <v>-6.630024279999998</v>
       </c>
       <c r="Q86">
-        <v>2.111881887999997</v>
+        <v>1.669975720000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3940383050799949</v>
+        <v>0.4172541920853279</v>
       </c>
       <c r="T86">
-        <v>4.538712514971574</v>
+        <v>4.841293349303013</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2833202191940267</v>
+        <v>0.2799870401446852</v>
       </c>
       <c r="W86">
-        <v>0.1052085918223169</v>
+        <v>0.1056979025067602</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8332947623353726</v>
+        <v>0.8234912945431918</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8754,22 +8754,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1524313459435454</v>
+        <v>0.1534413459435454</v>
       </c>
       <c r="C87">
-        <v>-99.26405324319654</v>
+        <v>-105.6999755089421</v>
       </c>
       <c r="D87">
-        <v>199.8209467568035</v>
+        <v>197.946024491058</v>
       </c>
       <c r="E87">
-        <v>-0.3149999999999977</v>
+        <v>4.246000000000038</v>
       </c>
       <c r="F87">
-        <v>387.685</v>
+        <v>392.246</v>
       </c>
       <c r="G87">
         <v>88.59999999999999</v>
@@ -8790,37 +8790,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M87">
-        <v>56.91215800000001</v>
+        <v>57.58171280000001</v>
       </c>
       <c r="N87">
-        <v>-10.04549133333333</v>
+        <v>-10.71504613333334</v>
       </c>
       <c r="O87">
-        <v>-3.415467053333333</v>
+        <v>-3.643115685333335</v>
       </c>
       <c r="P87">
-        <v>-6.630024279999998</v>
+        <v>-7.071930448000003</v>
       </c>
       <c r="Q87">
-        <v>1.669975720000003</v>
+        <v>1.228069551999997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4172541920853279</v>
+        <v>0.4437866343771371</v>
       </c>
       <c r="T87">
-        <v>4.841293349303013</v>
+        <v>5.18710001711037</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2799870401446852</v>
+        <v>0.2767313768871889</v>
       </c>
       <c r="W87">
-        <v>0.1056979025067602</v>
+        <v>0.1061758338729607</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8234912945431918</v>
+        <v>0.8139158143740848</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8836,22 +8836,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1534413459435454</v>
+        <v>0.1544513459435454</v>
       </c>
       <c r="C88">
-        <v>-105.6999755089421</v>
+        <v>-112.1010400106726</v>
       </c>
       <c r="D88">
-        <v>197.946024491058</v>
+        <v>196.1059599893274</v>
       </c>
       <c r="E88">
-        <v>4.246000000000038</v>
+        <v>8.807000000000016</v>
       </c>
       <c r="F88">
-        <v>392.246</v>
+        <v>396.807</v>
       </c>
       <c r="G88">
         <v>88.59999999999999</v>
@@ -8872,37 +8872,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M88">
-        <v>57.58171280000001</v>
+        <v>58.25126760000001</v>
       </c>
       <c r="N88">
-        <v>-10.71504613333334</v>
+        <v>-11.38460093333333</v>
       </c>
       <c r="O88">
-        <v>-3.643115685333335</v>
+        <v>-3.870764317333333</v>
       </c>
       <c r="P88">
-        <v>-7.071930448000003</v>
+        <v>-7.513836615999999</v>
       </c>
       <c r="Q88">
-        <v>1.228069551999997</v>
+        <v>0.7861633840000017</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4437866343771371</v>
+        <v>0.4744009908676862</v>
       </c>
       <c r="T88">
-        <v>5.18710001711037</v>
+        <v>5.586107710734246</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2767313768871889</v>
+        <v>0.2735505564631982</v>
       </c>
       <c r="W88">
-        <v>0.1061758338729607</v>
+        <v>0.1066427783112025</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8139158143740848</v>
+        <v>0.804560460185877</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8918,22 +8918,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1544513459435454</v>
+        <v>0.2076610908459769</v>
       </c>
       <c r="C89">
-        <v>-112.1010400106726</v>
+        <v>-181.1293437359886</v>
       </c>
       <c r="D89">
-        <v>196.1059599893274</v>
+        <v>131.6386562640114</v>
       </c>
       <c r="E89">
-        <v>8.807000000000016</v>
+        <v>13.36799999999999</v>
       </c>
       <c r="F89">
-        <v>396.807</v>
+        <v>401.368</v>
       </c>
       <c r="G89">
         <v>88.59999999999999</v>
@@ -8954,45 +8954,45 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M89">
-        <v>58.25126760000001</v>
+        <v>80.59469439999999</v>
       </c>
       <c r="N89">
-        <v>-11.38460093333333</v>
+        <v>-33.72802773333332</v>
       </c>
       <c r="O89">
-        <v>-3.870764317333333</v>
+        <v>-11.46752942933333</v>
       </c>
       <c r="P89">
-        <v>-7.513836615999999</v>
+        <v>-22.26049830399999</v>
       </c>
       <c r="Q89">
-        <v>0.7861633840000017</v>
+        <v>-13.96049830399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4744009908676862</v>
+        <v>0.5491156142935892</v>
       </c>
       <c r="T89">
-        <v>5.586107710734246</v>
+        <v>6.559889719915106</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.2735505564631982</v>
+        <v>0.1977135937457773</v>
       </c>
       <c r="W89">
-        <v>0.1066427783112025</v>
+        <v>0.1610991103758479</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.804560460185877</v>
+        <v>0.5815105698405214</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9000,22 +9000,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2076610908459769</v>
+        <v>0.2092110908459769</v>
       </c>
       <c r="C90">
-        <v>-181.1293437359886</v>
+        <v>-186.9389732883214</v>
       </c>
       <c r="D90">
-        <v>131.6386562640114</v>
+        <v>130.3900267116787</v>
       </c>
       <c r="E90">
-        <v>13.36799999999999</v>
+        <v>17.92900000000003</v>
       </c>
       <c r="F90">
-        <v>401.368</v>
+        <v>405.929</v>
       </c>
       <c r="G90">
         <v>88.59999999999999</v>
@@ -9036,37 +9036,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M90">
-        <v>80.59469439999999</v>
+        <v>81.51054320000001</v>
       </c>
       <c r="N90">
-        <v>-33.72802773333332</v>
+        <v>-34.64387653333334</v>
       </c>
       <c r="O90">
-        <v>-11.46752942933333</v>
+        <v>-11.77891802133334</v>
       </c>
       <c r="P90">
-        <v>-22.26049830399999</v>
+        <v>-22.864958512</v>
       </c>
       <c r="Q90">
-        <v>-13.96049830399999</v>
+        <v>-14.564958512</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5491156142935892</v>
+        <v>0.5948715792293701</v>
       </c>
       <c r="T90">
-        <v>6.559889719915106</v>
+        <v>7.15624333081648</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1977135937457773</v>
+        <v>0.1954920926924539</v>
       </c>
       <c r="W90">
-        <v>0.1610991103758479</v>
+        <v>0.1615451877873552</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5815105698405214</v>
+        <v>0.5749767432130997</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9082,22 +9082,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2092110908459769</v>
+        <v>0.2107610908459769</v>
       </c>
       <c r="C91">
-        <v>-186.9389732883214</v>
+        <v>-192.7251382067069</v>
       </c>
       <c r="D91">
-        <v>130.3900267116787</v>
+        <v>129.1648617932931</v>
       </c>
       <c r="E91">
-        <v>17.92900000000003</v>
+        <v>22.49000000000001</v>
       </c>
       <c r="F91">
-        <v>405.929</v>
+        <v>410.49</v>
       </c>
       <c r="G91">
         <v>88.59999999999999</v>
@@ -9118,37 +9118,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M91">
-        <v>81.51054320000001</v>
+        <v>82.42639200000001</v>
       </c>
       <c r="N91">
-        <v>-34.64387653333334</v>
+        <v>-35.55972533333333</v>
       </c>
       <c r="O91">
-        <v>-11.77891802133334</v>
+        <v>-12.09030661333333</v>
       </c>
       <c r="P91">
-        <v>-22.864958512</v>
+        <v>-23.46941872</v>
       </c>
       <c r="Q91">
-        <v>-14.564958512</v>
+        <v>-15.16941872</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5948715792293701</v>
+        <v>0.6497787371523071</v>
       </c>
       <c r="T91">
-        <v>7.15624333081648</v>
+        <v>7.871867663898128</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1954920926924539</v>
+        <v>0.1933199583292044</v>
       </c>
       <c r="W91">
-        <v>0.1615451877873552</v>
+        <v>0.1619813523674958</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5749767432130997</v>
+        <v>0.5685881127329542</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9164,22 +9164,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2107610908459769</v>
+        <v>0.2123110908459769</v>
       </c>
       <c r="C92">
-        <v>-192.7251382067069</v>
+        <v>-198.4884937661021</v>
       </c>
       <c r="D92">
-        <v>129.1648617932931</v>
+        <v>127.962506233898</v>
       </c>
       <c r="E92">
-        <v>22.49000000000001</v>
+        <v>27.05100000000004</v>
       </c>
       <c r="F92">
-        <v>410.49</v>
+        <v>415.051</v>
       </c>
       <c r="G92">
         <v>88.59999999999999</v>
@@ -9200,37 +9200,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M92">
-        <v>82.42639200000001</v>
+        <v>83.34224080000001</v>
       </c>
       <c r="N92">
-        <v>-35.55972533333333</v>
+        <v>-36.47557413333334</v>
       </c>
       <c r="O92">
-        <v>-12.09030661333333</v>
+        <v>-12.40169520533334</v>
       </c>
       <c r="P92">
-        <v>-23.46941872</v>
+        <v>-24.073878928</v>
       </c>
       <c r="Q92">
-        <v>-15.16941872</v>
+        <v>-15.773878928</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6497787371523071</v>
+        <v>0.7168874857247858</v>
       </c>
       <c r="T92">
-        <v>7.871867663898128</v>
+        <v>8.746519626553477</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1933199583292044</v>
+        <v>0.1911955631827296</v>
       </c>
       <c r="W92">
-        <v>0.1619813523674958</v>
+        <v>0.1624079309129079</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5685881127329542</v>
+        <v>0.5623398917139106</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9246,22 +9246,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2123110908459769</v>
+        <v>0.2138610908459769</v>
       </c>
       <c r="C93">
-        <v>-198.4884937661021</v>
+        <v>-204.2296710674877</v>
       </c>
       <c r="D93">
-        <v>127.962506233898</v>
+        <v>126.7823289325123</v>
       </c>
       <c r="E93">
-        <v>27.05100000000004</v>
+        <v>31.61200000000002</v>
       </c>
       <c r="F93">
-        <v>415.051</v>
+        <v>419.612</v>
       </c>
       <c r="G93">
         <v>88.59999999999999</v>
@@ -9282,37 +9282,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M93">
-        <v>83.34224080000001</v>
+        <v>84.25808960000001</v>
       </c>
       <c r="N93">
-        <v>-36.47557413333334</v>
+        <v>-37.39142293333333</v>
       </c>
       <c r="O93">
-        <v>-12.40169520533334</v>
+        <v>-12.71308379733333</v>
       </c>
       <c r="P93">
-        <v>-24.073878928</v>
+        <v>-24.678339136</v>
       </c>
       <c r="Q93">
-        <v>-15.773878928</v>
+        <v>-16.378339136</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7168874857247858</v>
+        <v>0.8007734214403843</v>
       </c>
       <c r="T93">
-        <v>8.746519626553477</v>
+        <v>9.839834579872665</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1911955631827296</v>
+        <v>0.1891173505394391</v>
       </c>
       <c r="W93">
-        <v>0.1624079309129079</v>
+        <v>0.1628252360116806</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5623398917139106</v>
+        <v>0.5562275015865856</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9328,22 +9328,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2138610908459769</v>
+        <v>0.2154110908459769</v>
       </c>
       <c r="C94">
-        <v>-204.2296710674877</v>
+        <v>-209.9492781424452</v>
       </c>
       <c r="D94">
-        <v>126.7823289325123</v>
+        <v>125.6237218575549</v>
       </c>
       <c r="E94">
-        <v>31.61200000000002</v>
+        <v>36.17300000000006</v>
       </c>
       <c r="F94">
-        <v>419.612</v>
+        <v>424.1730000000001</v>
       </c>
       <c r="G94">
         <v>88.59999999999999</v>
@@ -9364,37 +9364,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M94">
-        <v>84.25808960000001</v>
+        <v>85.17393840000001</v>
       </c>
       <c r="N94">
-        <v>-37.39142293333333</v>
+        <v>-38.30727173333334</v>
       </c>
       <c r="O94">
-        <v>-12.71308379733333</v>
+        <v>-13.02447238933333</v>
       </c>
       <c r="P94">
-        <v>-24.678339136</v>
+        <v>-25.282799344</v>
       </c>
       <c r="Q94">
-        <v>-16.378339136</v>
+        <v>-16.982799344</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8007734214403843</v>
+        <v>0.9086267673604392</v>
       </c>
       <c r="T94">
-        <v>9.839834579872665</v>
+        <v>11.24552523414019</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1891173505394391</v>
+        <v>0.1870838306411656</v>
       </c>
       <c r="W94">
-        <v>0.1628252360116806</v>
+        <v>0.163233566807254</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5562275015865856</v>
+        <v>0.5502465607093104</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9410,22 +9410,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2154110908459769</v>
+        <v>0.2169610908459769</v>
       </c>
       <c r="C95">
-        <v>-209.9492781424452</v>
+        <v>-215.6479009977145</v>
       </c>
       <c r="D95">
-        <v>125.6237218575549</v>
+        <v>124.4860990022856</v>
       </c>
       <c r="E95">
-        <v>36.17300000000006</v>
+        <v>40.73400000000004</v>
       </c>
       <c r="F95">
-        <v>424.1730000000001</v>
+        <v>428.734</v>
       </c>
       <c r="G95">
         <v>88.59999999999999</v>
@@ -9446,37 +9446,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M95">
-        <v>85.17393840000001</v>
+        <v>86.0897872</v>
       </c>
       <c r="N95">
-        <v>-38.30727173333334</v>
+        <v>-39.22312053333333</v>
       </c>
       <c r="O95">
-        <v>-13.02447238933333</v>
+        <v>-13.33586098133333</v>
       </c>
       <c r="P95">
-        <v>-25.282799344</v>
+        <v>-25.887259552</v>
       </c>
       <c r="Q95">
-        <v>-16.982799344</v>
+        <v>-17.587259552</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9086267673604392</v>
+        <v>1.05243122858718</v>
       </c>
       <c r="T95">
-        <v>11.24552523414019</v>
+        <v>13.11977943983022</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1870838306411656</v>
+        <v>0.1850935771237064</v>
       </c>
       <c r="W95">
-        <v>0.163233566807254</v>
+        <v>0.1636332097135598</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5502465607093104</v>
+        <v>0.544392873893254</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9492,22 +9492,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2169610908459769</v>
+        <v>0.2185110908459769</v>
       </c>
       <c r="C96">
-        <v>-215.6479009977145</v>
+        <v>-221.3261046035074</v>
       </c>
       <c r="D96">
-        <v>124.4860990022856</v>
+        <v>123.3688953964927</v>
       </c>
       <c r="E96">
-        <v>40.73400000000004</v>
+        <v>45.29500000000007</v>
       </c>
       <c r="F96">
-        <v>428.734</v>
+        <v>433.2950000000001</v>
       </c>
       <c r="G96">
         <v>88.59999999999999</v>
@@ -9528,37 +9528,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M96">
-        <v>86.0897872</v>
+        <v>87.00563600000002</v>
       </c>
       <c r="N96">
-        <v>-39.22312053333333</v>
+        <v>-40.13896933333335</v>
       </c>
       <c r="O96">
-        <v>-13.33586098133333</v>
+        <v>-13.64724957333334</v>
       </c>
       <c r="P96">
-        <v>-25.887259552</v>
+        <v>-26.49171976000001</v>
       </c>
       <c r="Q96">
-        <v>-17.587259552</v>
+        <v>-18.19171976000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.05243122858718</v>
+        <v>1.253757474304616</v>
       </c>
       <c r="T96">
-        <v>13.11977943983022</v>
+        <v>15.74373532779628</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1850935771237064</v>
+        <v>0.1831452236802989</v>
       </c>
       <c r="W96">
-        <v>0.1636332097135598</v>
+        <v>0.164024439084996</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.544392873893254</v>
+        <v>0.5386624225891143</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9574,22 +9574,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2185110908459769</v>
+        <v>0.2200610908459769</v>
       </c>
       <c r="C97">
-        <v>-221.3261046035074</v>
+        <v>-226.9844338290748</v>
       </c>
       <c r="D97">
-        <v>123.3688953964927</v>
+        <v>122.2715661709252</v>
       </c>
       <c r="E97">
-        <v>45.29500000000007</v>
+        <v>49.85600000000005</v>
       </c>
       <c r="F97">
-        <v>433.2950000000001</v>
+        <v>437.8560000000001</v>
       </c>
       <c r="G97">
         <v>88.59999999999999</v>
@@ -9610,37 +9610,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M97">
-        <v>87.00563600000002</v>
+        <v>87.92148480000002</v>
       </c>
       <c r="N97">
-        <v>-40.13896933333335</v>
+        <v>-41.05481813333334</v>
       </c>
       <c r="O97">
-        <v>-13.64724957333334</v>
+        <v>-13.95863816533334</v>
       </c>
       <c r="P97">
-        <v>-26.49171976000001</v>
+        <v>-27.096179968</v>
       </c>
       <c r="Q97">
-        <v>-18.19171976000001</v>
+        <v>-18.796179968</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.253757474304616</v>
+        <v>1.555746842880771</v>
       </c>
       <c r="T97">
-        <v>15.74373532779628</v>
+        <v>19.67966915974536</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1831452236802989</v>
+        <v>0.1812374609336291</v>
       </c>
       <c r="W97">
-        <v>0.164024439084996</v>
+        <v>0.1644075178445273</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5386624225891143</v>
+        <v>0.5330513556871445</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9656,22 +9656,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2200610908459769</v>
+        <v>0.2216110908459769</v>
       </c>
       <c r="C98">
-        <v>-226.9844338290748</v>
+        <v>-232.6234143287861</v>
       </c>
       <c r="D98">
-        <v>122.2715661709252</v>
+        <v>121.193585671214</v>
       </c>
       <c r="E98">
-        <v>49.85599999999999</v>
+        <v>54.41700000000003</v>
       </c>
       <c r="F98">
-        <v>437.856</v>
+        <v>442.417</v>
       </c>
       <c r="G98">
         <v>88.59999999999999</v>
@@ -9692,37 +9692,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M98">
-        <v>87.9214848</v>
+        <v>88.83733360000001</v>
       </c>
       <c r="N98">
-        <v>-41.05481813333333</v>
+        <v>-41.97066693333333</v>
       </c>
       <c r="O98">
-        <v>-13.95863816533333</v>
+        <v>-14.27002675733334</v>
       </c>
       <c r="P98">
-        <v>-27.09617996799999</v>
+        <v>-27.700640176</v>
       </c>
       <c r="Q98">
-        <v>-18.79617996799999</v>
+        <v>-19.400640176</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.555746842880767</v>
+        <v>2.059062457174355</v>
       </c>
       <c r="T98">
-        <v>19.6796691597453</v>
+        <v>26.2395588796604</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1812374609336292</v>
+        <v>0.1793690335013237</v>
       </c>
       <c r="W98">
-        <v>0.1644075178445273</v>
+        <v>0.1647826980729342</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5330513556871446</v>
+        <v>0.5275559808862461</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9738,22 +9738,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2216110908459769</v>
+        <v>0.2231610908459769</v>
       </c>
       <c r="C99">
-        <v>-232.6234143287861</v>
+        <v>-238.2435533817451</v>
       </c>
       <c r="D99">
-        <v>121.193585671214</v>
+        <v>120.1344466182549</v>
       </c>
       <c r="E99">
-        <v>54.41700000000003</v>
+        <v>58.97800000000001</v>
       </c>
       <c r="F99">
-        <v>442.417</v>
+        <v>446.978</v>
       </c>
       <c r="G99">
         <v>88.59999999999999</v>
@@ -9774,37 +9774,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M99">
-        <v>88.83733360000001</v>
+        <v>89.7531824</v>
       </c>
       <c r="N99">
-        <v>-41.97066693333333</v>
+        <v>-42.88651573333333</v>
       </c>
       <c r="O99">
-        <v>-14.27002675733334</v>
+        <v>-14.58141534933333</v>
       </c>
       <c r="P99">
-        <v>-27.700640176</v>
+        <v>-28.30510038399999</v>
       </c>
       <c r="Q99">
-        <v>-19.400640176</v>
+        <v>-20.00510038399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.059062457174355</v>
+        <v>3.065693685761532</v>
       </c>
       <c r="T99">
-        <v>26.2395588796604</v>
+        <v>39.3593383194906</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1793690335013237</v>
+        <v>0.1775387372411061</v>
       </c>
       <c r="W99">
-        <v>0.1647826980729342</v>
+        <v>0.1651502215619859</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5275559808862461</v>
+        <v>0.5221727565914885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9820,22 +9820,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2231610908459769</v>
+        <v>0.2247110908459769</v>
       </c>
       <c r="C100">
-        <v>-238.2435533817451</v>
+        <v>-243.8453406877629</v>
       </c>
       <c r="D100">
-        <v>120.1344466182549</v>
+        <v>119.0936593122371</v>
       </c>
       <c r="E100">
-        <v>58.97800000000001</v>
+        <v>63.53900000000004</v>
       </c>
       <c r="F100">
-        <v>446.978</v>
+        <v>451.539</v>
       </c>
       <c r="G100">
         <v>88.59999999999999</v>
@@ -9856,37 +9856,37 @@
         <v>46.86666666666667</v>
       </c>
       <c r="M100">
-        <v>89.7531824</v>
+        <v>90.66903120000001</v>
       </c>
       <c r="N100">
-        <v>-42.88651573333333</v>
+        <v>-43.80236453333333</v>
       </c>
       <c r="O100">
-        <v>-14.58141534933333</v>
+        <v>-14.89280394133333</v>
       </c>
       <c r="P100">
-        <v>-28.30510038399999</v>
+        <v>-28.909560592</v>
       </c>
       <c r="Q100">
-        <v>-20.00510038399999</v>
+        <v>-20.609560592</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.065693685761532</v>
+        <v>6.085587371523066</v>
       </c>
       <c r="T100">
-        <v>39.3593383194906</v>
+        <v>78.71867663898121</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1775387372411061</v>
+        <v>0.1757454166629131</v>
       </c>
       <c r="W100">
-        <v>0.1651502215619859</v>
+        <v>0.1655103203340871</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9894,91 +9894,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5221727565914885</v>
+        <v>0.5168982843026856</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2247110908459769</v>
-      </c>
-      <c r="C101">
-        <v>-243.8453406877629</v>
-      </c>
-      <c r="D101">
-        <v>119.0936593122371</v>
-      </c>
-      <c r="E101">
-        <v>63.53900000000004</v>
-      </c>
-      <c r="F101">
-        <v>451.539</v>
-      </c>
-      <c r="G101">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="H101">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>55.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L101">
-        <v>46.86666666666667</v>
-      </c>
-      <c r="M101">
-        <v>90.66903120000001</v>
-      </c>
-      <c r="N101">
-        <v>-43.80236453333333</v>
-      </c>
-      <c r="O101">
-        <v>-14.89280394133333</v>
-      </c>
-      <c r="P101">
-        <v>-28.909560592</v>
-      </c>
-      <c r="Q101">
-        <v>-20.609560592</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.085587371523066</v>
-      </c>
-      <c r="T101">
-        <v>78.71867663898121</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1757454166629131</v>
-      </c>
-      <c r="W101">
-        <v>0.1655103203340871</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5168982843026856</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
